--- a/BPCOME-3502单片机需求260724a.xlsx
+++ b/BPCOME-3502单片机需求260724a.xlsx
@@ -1412,7 +1412,7 @@
     <t>PWROK</t>
   </si>
   <si>
-    <t>底板电源OK信号输出，参考PB6高后输出高</t>
+    <t xml:space="preserve">底板电源OK信号输出，参考PB6高后输出高  </t>
   </si>
   <si>
     <t xml:space="preserve">PB14 </t>

--- a/BPCOME-3502单片机需求260724a.xlsx
+++ b/BPCOME-3502单片机需求260724a.xlsx
@@ -1439,7 +1439,7 @@
     <t>SLP_S3#</t>
   </si>
   <si>
-    <t>核心卡S3睡眠信号输入，低有效</t>
+    <t>核心卡S3睡眠信号输入，低有效  改成了自检，高表示开机低表示关机</t>
   </si>
   <si>
     <t xml:space="preserve">PC1 </t>
@@ -1611,14 +1611,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1819,7 +1812,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2020,12 +2013,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2219,214 +2206,214 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2458,17 +2445,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2477,26 +2464,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -7146,7 +7133,7 @@
       <c r="F38" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="10" t="s">
         <v>449</v>
       </c>
       <c r="H38" s="11"/>

--- a/BPCOME-3502单片机需求260724a.xlsx
+++ b/BPCOME-3502单片机需求260724a.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LYT\潘工\BPCOME-3502-git\BPCOME-3502\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="22188" windowHeight="9180" firstSheet="2" activeTab="2"/>
   </bookViews>
@@ -33,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="503">
   <si>
     <t>当前PIN</t>
   </si>
@@ -1337,7 +1342,7 @@
     <t>GD_PWRBTIN#</t>
   </si>
   <si>
-    <t>预留，开关机信号输入，低有效</t>
+    <t>开关机信号输入，低有效</t>
   </si>
   <si>
     <t xml:space="preserve">PB5 </t>
@@ -1346,7 +1351,7 @@
     <t>PWRBTN_OUT#</t>
   </si>
   <si>
-    <t>预留，做输出给核心卡，后续需要延时开关机使用</t>
+    <t>做输出给核心卡，当接收到PB4有20ms低电平或以上，就输出20ms低电平脉冲</t>
   </si>
   <si>
     <t xml:space="preserve">PB6 </t>
@@ -1833,6 +1838,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="3"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1936,12 +1947,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2212,7 +2217,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2236,16 +2241,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2254,42 +2259,42 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -2323,7 +2328,7 @@
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2336,7 +2341,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2389,6 +2394,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2408,7 +2416,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2420,23 +2428,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3197,1629 +3205,1629 @@
   <dimension ref="A1:G93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="12.3333333333333" style="50" customWidth="1"/>
-    <col min="2" max="2" width="13" style="50" customWidth="1"/>
+    <col min="1" max="1" width="12.3333333333333" style="51" customWidth="1"/>
+    <col min="2" max="2" width="13" style="51" customWidth="1"/>
     <col min="3" max="3" width="23.7314814814815" customWidth="1"/>
-    <col min="4" max="4" width="9.73148148148148" style="26" customWidth="1"/>
-    <col min="5" max="5" width="10.7314814814815" style="26" customWidth="1"/>
+    <col min="4" max="4" width="9.73148148148148" style="27" customWidth="1"/>
+    <col min="5" max="5" width="10.7314814814815" style="27" customWidth="1"/>
     <col min="6" max="6" width="70" customWidth="1"/>
     <col min="7" max="7" width="95.6018518518518" customWidth="1"/>
     <col min="8" max="8" width="31.6018518518519" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="49" customFormat="1" ht="22.2" spans="1:7">
-      <c r="A1" s="51" t="s">
+    <row r="1" s="50" customFormat="1" ht="22.2" spans="1:7">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="53" t="s">
+      <c r="E1" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="52" t="s">
+      <c r="G1" s="53" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="36" t="s">
+      <c r="D2" s="31"/>
+      <c r="E2" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="54" t="s">
+      <c r="A3" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="36" t="s">
+      <c r="D3" s="31"/>
+      <c r="E3" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="36" t="s">
+      <c r="D4" s="31"/>
+      <c r="E4" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="36" t="s">
+      <c r="D5" s="31"/>
+      <c r="E5" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="29"/>
+      <c r="G6" s="30"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="29"/>
+      <c r="G7" s="30"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="29"/>
+      <c r="G8" s="30"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="D9" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="E9" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="29"/>
+      <c r="G9" s="30"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="29"/>
+      <c r="G10" s="30"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="29"/>
+      <c r="G11" s="30"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="29"/>
+      <c r="G12" s="30"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="54"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="E15" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="30" t="s">
+      <c r="E16" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="30" t="s">
+      <c r="D17" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="30" t="s">
+      <c r="E17" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="29"/>
+      <c r="G17" s="30"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="54"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
+      <c r="A18" s="55"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="54" t="s">
+      <c r="A19" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="30" t="s">
+      <c r="E19" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="29" t="s">
+      <c r="F19" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="G19" s="29"/>
+      <c r="G19" s="30"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="54" t="s">
+      <c r="B20" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="30"/>
-      <c r="E20" s="36" t="s">
+      <c r="D20" s="31"/>
+      <c r="E20" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="54" t="s">
+      <c r="A21" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="54" t="s">
+      <c r="B21" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="30" t="s">
+      <c r="E21" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="29" t="s">
+      <c r="F21" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="29"/>
+      <c r="G21" s="30"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="54" t="s">
+      <c r="B22" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="30" t="s">
+      <c r="E22" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="29" t="s">
+      <c r="F22" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="G22" s="29"/>
+      <c r="G22" s="30"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="54" t="s">
+      <c r="A23" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="D23" s="30" t="s">
+      <c r="D23" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="30" t="s">
+      <c r="E23" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="29" t="s">
+      <c r="F23" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="G23" s="29"/>
+      <c r="G23" s="30"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="54" t="s">
+      <c r="A24" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="30" t="s">
+      <c r="E24" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="29" t="s">
+      <c r="F24" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="G24" s="29"/>
+      <c r="G24" s="30"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="54" t="s">
+      <c r="A25" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="30" t="s">
+      <c r="D25" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="30" t="s">
+      <c r="E25" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="F25" s="29" t="s">
+      <c r="F25" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="G25" s="29"/>
+      <c r="G25" s="30"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="54" t="s">
+      <c r="A26" s="55" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E26" s="30" t="s">
+      <c r="E26" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="29" t="s">
+      <c r="F26" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="G26" s="29"/>
+      <c r="G26" s="30"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="54" t="s">
+      <c r="A27" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="54" t="s">
+      <c r="B27" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D27" s="30" t="s">
+      <c r="D27" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E27" s="30" t="s">
+      <c r="E27" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="F27" s="29" t="s">
+      <c r="F27" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="G27" s="29"/>
+      <c r="G27" s="30"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="54" t="s">
+      <c r="A28" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="54" t="s">
+      <c r="B28" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="30" t="s">
+      <c r="D28" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E28" s="30" t="s">
+      <c r="E28" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="G28" s="29"/>
+      <c r="G28" s="30"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="54" t="s">
+      <c r="A29" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="B29" s="54" t="s">
+      <c r="B29" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D29" s="30" t="s">
+      <c r="D29" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="30" t="s">
+      <c r="E29" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="29" t="s">
+      <c r="F29" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="G29" s="29"/>
+      <c r="G29" s="30"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="54" t="s">
+      <c r="A30" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="54" t="s">
+      <c r="B30" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="30" t="s">
+      <c r="D30" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="30" t="s">
+      <c r="E30" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F30" s="29" t="s">
+      <c r="F30" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="G30" s="29"/>
+      <c r="G30" s="30"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="54" t="s">
+      <c r="A31" s="55" t="s">
         <v>97</v>
       </c>
-      <c r="B31" s="54" t="s">
+      <c r="B31" s="55" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="30" t="s">
+      <c r="D31" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="36" t="s">
+      <c r="E31" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F31" s="29" t="s">
+      <c r="F31" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="G31" s="29"/>
+      <c r="G31" s="30"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="54" t="s">
+      <c r="A32" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="54" t="s">
+      <c r="B32" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="30" t="s">
+      <c r="D32" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="36" t="s">
+      <c r="E32" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F32" s="29" t="s">
+      <c r="F32" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="G32" s="29"/>
+      <c r="G32" s="30"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="54" t="s">
+      <c r="A33" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="54" t="s">
+      <c r="B33" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="30" t="s">
+      <c r="D33" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E33" s="36" t="s">
+      <c r="E33" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F33" s="29" t="s">
+      <c r="F33" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="G33" s="29"/>
+      <c r="G33" s="30"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="54" t="s">
+      <c r="A34" s="55" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="54"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
+      <c r="B34" s="55"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="54"/>
-      <c r="B35" s="54"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
+      <c r="A35" s="55"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="54" t="s">
+      <c r="A36" s="55" t="s">
         <v>107</v>
       </c>
-      <c r="B36" s="54" t="s">
+      <c r="B36" s="55" t="s">
         <v>107</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="D36" s="30"/>
-      <c r="E36" s="36" t="s">
+      <c r="D36" s="31"/>
+      <c r="E36" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="54" t="s">
+      <c r="A37" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="54" t="s">
+      <c r="B37" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="30"/>
-      <c r="E37" s="36" t="s">
+      <c r="D37" s="31"/>
+      <c r="E37" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="54" t="s">
+      <c r="A38" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="54" t="s">
+      <c r="B38" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="D38" s="30"/>
-      <c r="E38" s="36" t="s">
+      <c r="D38" s="31"/>
+      <c r="E38" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="54" t="s">
+      <c r="A39" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="54" t="s">
+      <c r="B39" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="55" t="s">
+      <c r="C39" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D39" s="30" t="s">
+      <c r="D39" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E39" s="36" t="s">
+      <c r="E39" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="F39" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="G39" s="29"/>
+      <c r="G39" s="30"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="54" t="s">
+      <c r="A40" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="54" t="s">
+      <c r="B40" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="D40" s="30"/>
-      <c r="E40" s="36" t="s">
+      <c r="D40" s="31"/>
+      <c r="E40" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="54" t="s">
+      <c r="A41" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="B41" s="54" t="s">
+      <c r="B41" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="D41" s="30"/>
-      <c r="E41" s="36" t="s">
+      <c r="D41" s="31"/>
+      <c r="E41" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="54" t="s">
+      <c r="A42" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="B42" s="54"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="29"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="30"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="54" t="s">
+      <c r="A43" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="B43" s="54"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
+      <c r="B43" s="55"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="54" t="s">
+      <c r="A44" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="54" t="s">
+      <c r="B44" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="D44" s="30" t="s">
+      <c r="D44" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E44" s="30" t="s">
+      <c r="E44" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F44" s="29" t="s">
+      <c r="F44" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="G44" s="29"/>
+      <c r="G44" s="30"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="54" t="s">
+      <c r="A45" s="55" t="s">
         <v>123</v>
       </c>
-      <c r="B45" s="54" t="s">
+      <c r="B45" s="55" t="s">
         <v>123</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="D45" s="30" t="s">
+      <c r="D45" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E45" s="30" t="s">
+      <c r="E45" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F45" s="29" t="s">
+      <c r="F45" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="G45" s="29"/>
+      <c r="G45" s="30"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="54" t="s">
+      <c r="A46" s="55" t="s">
         <v>126</v>
       </c>
-      <c r="B46" s="54" t="s">
+      <c r="B46" s="55" t="s">
         <v>127</v>
       </c>
-      <c r="C46" s="29" t="s">
+      <c r="C46" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="D46" s="30" t="s">
+      <c r="D46" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E46" s="30" t="s">
+      <c r="E46" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="F46" s="29" t="s">
+      <c r="F46" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="G46" s="29"/>
+      <c r="G46" s="30"/>
     </row>
     <row r="47" ht="14.65" customHeight="1" spans="1:7">
-      <c r="A47" s="54" t="s">
+      <c r="A47" s="55" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="54" t="s">
+      <c r="B47" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="D47" s="30" t="s">
+      <c r="D47" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E47" s="30" t="s">
+      <c r="E47" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="29" t="s">
+      <c r="F47" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="G47" s="29"/>
+      <c r="G47" s="30"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="54" t="s">
+      <c r="A48" s="55" t="s">
         <v>134</v>
       </c>
-      <c r="B48" s="54"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
+      <c r="B48" s="55"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="54" t="s">
+      <c r="A49" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="B49" s="54"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
+      <c r="B49" s="55"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="54" t="s">
+      <c r="A50" s="55" t="s">
         <v>136</v>
       </c>
-      <c r="B50" s="54"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="29"/>
+      <c r="B50" s="55"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="31"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="54" t="s">
+      <c r="A51" s="55" t="s">
         <v>137</v>
       </c>
-      <c r="B51" s="54"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
+      <c r="B51" s="55"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="54"/>
-      <c r="B52" s="54"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
+      <c r="A52" s="55"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="54" t="s">
+      <c r="A53" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="B53" s="54" t="s">
+      <c r="B53" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="D53" s="30"/>
-      <c r="E53" s="36" t="s">
+      <c r="D53" s="31"/>
+      <c r="E53" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F53" s="57" t="s">
+      <c r="F53" s="58" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="29"/>
+      <c r="G53" s="30"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="54" t="s">
+      <c r="A54" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="B54" s="54" t="s">
+      <c r="B54" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="D54" s="30" t="s">
+      <c r="D54" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E54" s="30" t="s">
+      <c r="E54" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F54" s="29" t="s">
+      <c r="F54" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="G54" s="29"/>
+      <c r="G54" s="30"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="54" t="s">
+      <c r="A55" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="B55" s="54" t="s">
+      <c r="B55" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="D55" s="30" t="s">
+      <c r="D55" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E55" s="30" t="s">
+      <c r="E55" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F55" s="29" t="s">
+      <c r="F55" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="G55" s="29"/>
+      <c r="G55" s="30"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="54" t="s">
+      <c r="A56" s="55" t="s">
         <v>148</v>
       </c>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="29"/>
+      <c r="D56" s="31"/>
+      <c r="E56" s="31"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="54" t="s">
+      <c r="A57" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="B57" s="54" t="s">
+      <c r="B57" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="C57" s="29" t="s">
+      <c r="C57" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="D57" s="30" t="s">
+      <c r="D57" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E57" s="30" t="s">
+      <c r="E57" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="F57" s="57" t="s">
+      <c r="F57" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="G57" s="29"/>
+      <c r="G57" s="30"/>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="54" t="s">
+      <c r="A58" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="B58" s="54" t="s">
+      <c r="B58" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30" t="s">
+      <c r="D58" s="31"/>
+      <c r="E58" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="F58" s="35" t="s">
+      <c r="F58" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="G58" s="58" t="s">
+      <c r="G58" s="59" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="54" t="s">
+      <c r="A59" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="B59" s="54" t="s">
+      <c r="B59" s="55" t="s">
         <v>159</v>
       </c>
-      <c r="C59" s="29" t="s">
+      <c r="C59" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30" t="s">
+      <c r="D59" s="31"/>
+      <c r="E59" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="F59" s="35" t="s">
+      <c r="F59" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="G59" s="59"/>
+      <c r="G59" s="60"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="54" t="s">
+      <c r="A60" s="55" t="s">
         <v>162</v>
       </c>
-      <c r="B60" s="54" t="s">
+      <c r="B60" s="55" t="s">
         <v>162</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30" t="s">
+      <c r="D60" s="31"/>
+      <c r="E60" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="F60" s="35" t="s">
+      <c r="F60" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="G60" s="59"/>
+      <c r="G60" s="60"/>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="54" t="s">
+      <c r="A61" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="B61" s="54" t="s">
+      <c r="B61" s="55" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="D61" s="30" t="s">
+      <c r="D61" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E61" s="30" t="s">
+      <c r="E61" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="F61" s="35" t="s">
+      <c r="F61" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="G61" s="59"/>
+      <c r="G61" s="60"/>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="54" t="s">
+      <c r="A62" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="B62" s="54" t="s">
+      <c r="B62" s="55" t="s">
         <v>168</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="D62" s="30" t="s">
+      <c r="D62" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E62" s="30" t="s">
+      <c r="E62" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="F62" s="35" t="s">
+      <c r="F62" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="G62" s="60"/>
+      <c r="G62" s="61"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="54" t="s">
+      <c r="A63" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="54"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="30"/>
-      <c r="E63" s="30"/>
-      <c r="F63" s="29"/>
-      <c r="G63" s="29"/>
+      <c r="B63" s="55"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="31"/>
+      <c r="E63" s="31"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="54" t="s">
+      <c r="A64" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="B64" s="54"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
+      <c r="B64" s="55"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="54" t="s">
+      <c r="A65" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="B65" s="54" t="s">
+      <c r="B65" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C65" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="D65" s="30" t="s">
+      <c r="D65" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E65" s="30" t="s">
+      <c r="E65" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F65" s="29" t="s">
+      <c r="F65" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="G65" s="29"/>
+      <c r="G65" s="30"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="54" t="s">
+      <c r="A66" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="54"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="30"/>
-      <c r="F66" s="29"/>
-      <c r="G66" s="29"/>
+      <c r="B66" s="55"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="31"/>
+      <c r="E66" s="31"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="54" t="s">
+      <c r="A67" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="B67" s="54" t="s">
+      <c r="B67" s="55" t="s">
         <v>136</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="C67" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="D67" s="30" t="s">
+      <c r="D67" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E67" s="30" t="s">
+      <c r="E67" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F67" s="29" t="s">
+      <c r="F67" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="G67" s="29"/>
+      <c r="G67" s="30"/>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="54" t="s">
+      <c r="A68" s="55" t="s">
         <v>159</v>
       </c>
-      <c r="B68" s="54" t="s">
+      <c r="B68" s="55" t="s">
         <v>137</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="D68" s="30" t="s">
+      <c r="D68" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E68" s="30" t="s">
+      <c r="E68" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F68" s="29" t="s">
+      <c r="F68" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="G68" s="29"/>
+      <c r="G68" s="30"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="54"/>
-      <c r="B69" s="54"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="30"/>
-      <c r="E69" s="30"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
+      <c r="A69" s="55"/>
+      <c r="B69" s="55"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="54" t="s">
+      <c r="A70" s="55" t="s">
         <v>177</v>
       </c>
-      <c r="B70" s="54" t="s">
+      <c r="B70" s="55" t="s">
         <v>178</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="C70" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="D70" s="30" t="s">
+      <c r="D70" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E70" s="30" t="s">
+      <c r="E70" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="F70" s="29" t="s">
+      <c r="F70" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="G70" s="29" t="s">
+      <c r="G70" s="30" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="54" t="s">
+      <c r="A71" s="55" t="s">
         <v>182</v>
       </c>
-      <c r="B71" s="54" t="s">
+      <c r="B71" s="55" t="s">
         <v>183</v>
       </c>
-      <c r="C71" s="29" t="s">
+      <c r="C71" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="D71" s="30" t="s">
+      <c r="D71" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E71" s="30" t="s">
+      <c r="E71" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="F71" s="29" t="s">
+      <c r="F71" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="G71" s="29" t="s">
+      <c r="G71" s="30" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="54" t="s">
+      <c r="A72" s="55" t="s">
         <v>186</v>
       </c>
-      <c r="B72" s="54" t="s">
+      <c r="B72" s="55" t="s">
         <v>186</v>
       </c>
-      <c r="C72" s="29" t="s">
+      <c r="C72" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="D72" s="30" t="s">
+      <c r="D72" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E72" s="30" t="s">
+      <c r="E72" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="29" t="s">
+      <c r="F72" s="30" t="s">
         <v>188</v>
       </c>
-      <c r="G72" s="29"/>
+      <c r="G72" s="30"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="54" t="s">
+      <c r="A73" s="55" t="s">
         <v>189</v>
       </c>
-      <c r="B73" s="54" t="s">
+      <c r="B73" s="55" t="s">
         <v>189</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C73" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="D73" s="30" t="s">
+      <c r="D73" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E73" s="30" t="s">
+      <c r="E73" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="F73" s="29" t="s">
+      <c r="F73" s="30" t="s">
         <v>188</v>
       </c>
-      <c r="G73" s="29"/>
+      <c r="G73" s="30"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="54" t="s">
+      <c r="A74" s="55" t="s">
         <v>191</v>
       </c>
-      <c r="B74" s="54" t="s">
+      <c r="B74" s="55" t="s">
         <v>191</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="D74" s="30" t="s">
+      <c r="D74" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E74" s="36" t="s">
+      <c r="E74" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F74" s="29" t="s">
+      <c r="F74" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="G74" s="29"/>
+      <c r="G74" s="30"/>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="54" t="s">
+      <c r="A75" s="55" t="s">
         <v>194</v>
       </c>
-      <c r="B75" s="54" t="s">
+      <c r="B75" s="55" t="s">
         <v>194</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C75" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30" t="s">
+      <c r="D75" s="31"/>
+      <c r="E75" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="F75" s="35" t="s">
+      <c r="F75" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="G75" s="57" t="s">
+      <c r="G75" s="58" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="54" t="s">
+      <c r="A76" s="55" t="s">
         <v>197</v>
       </c>
-      <c r="B76" s="54" t="s">
+      <c r="B76" s="55" t="s">
         <v>197</v>
       </c>
-      <c r="C76" s="29" t="s">
+      <c r="C76" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="D76" s="30" t="s">
+      <c r="D76" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E76" s="30" t="s">
+      <c r="E76" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="F76" s="29" t="s">
+      <c r="F76" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="G76" s="29"/>
+      <c r="G76" s="30"/>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="54" t="s">
+      <c r="A77" s="55" t="s">
         <v>200</v>
       </c>
-      <c r="B77" s="54" t="s">
+      <c r="B77" s="55" t="s">
         <v>200</v>
       </c>
-      <c r="C77" s="29" t="s">
+      <c r="C77" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="D77" s="30" t="s">
+      <c r="D77" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E77" s="30" t="s">
+      <c r="E77" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F77" s="29" t="s">
+      <c r="F77" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="G77" s="29"/>
+      <c r="G77" s="30"/>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="54" t="s">
+      <c r="A78" s="55" t="s">
         <v>203</v>
       </c>
-      <c r="B78" s="54" t="s">
+      <c r="B78" s="55" t="s">
         <v>80</v>
       </c>
-      <c r="C78" s="29" t="s">
+      <c r="C78" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="D78" s="30" t="s">
+      <c r="D78" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E78" s="30" t="s">
+      <c r="E78" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="F78" s="29" t="s">
+      <c r="F78" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="G78" s="29"/>
+      <c r="G78" s="30"/>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="54" t="s">
+      <c r="A79" s="55" t="s">
         <v>206</v>
       </c>
-      <c r="B79" s="54" t="s">
+      <c r="B79" s="55" t="s">
         <v>206</v>
       </c>
-      <c r="C79" s="29" t="s">
+      <c r="C79" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="D79" s="30" t="s">
+      <c r="D79" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E79" s="30" t="s">
+      <c r="E79" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="F79" s="29" t="s">
+      <c r="F79" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="G79" s="29"/>
+      <c r="G79" s="30"/>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="54" t="s">
+      <c r="A80" s="55" t="s">
         <v>209</v>
       </c>
-      <c r="B80" s="54" t="s">
+      <c r="B80" s="55" t="s">
         <v>210</v>
       </c>
-      <c r="C80" s="29" t="s">
+      <c r="C80" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="D80" s="30" t="s">
+      <c r="D80" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E80" s="30" t="s">
+      <c r="E80" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="F80" s="29" t="s">
+      <c r="F80" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="G80" s="29"/>
+      <c r="G80" s="30"/>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" s="54" t="s">
+      <c r="A81" s="55" t="s">
         <v>210</v>
       </c>
-      <c r="B81" s="54" t="s">
+      <c r="B81" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="C81" s="29" t="s">
+      <c r="C81" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="D81" s="30" t="s">
+      <c r="D81" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E81" s="30" t="s">
+      <c r="E81" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="F81" s="29" t="s">
+      <c r="F81" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="G81" s="29"/>
+      <c r="G81" s="30"/>
     </row>
     <row r="82" spans="1:7">
-      <c r="A82" s="54" t="s">
+      <c r="A82" s="55" t="s">
         <v>217</v>
       </c>
-      <c r="B82" s="54" t="s">
+      <c r="B82" s="55" t="s">
         <v>218</v>
       </c>
-      <c r="C82" s="29" t="s">
+      <c r="C82" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="D82" s="30" t="s">
+      <c r="D82" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E82" s="30" t="s">
+      <c r="E82" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="F82" s="29" t="s">
+      <c r="F82" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="G82" s="29"/>
+      <c r="G82" s="30"/>
     </row>
     <row r="83" spans="1:7">
-      <c r="A83" s="54" t="s">
+      <c r="A83" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="B83" s="54" t="s">
+      <c r="B83" s="55" t="s">
         <v>220</v>
       </c>
-      <c r="C83" s="35" t="s">
+      <c r="C83" s="36" t="s">
         <v>221</v>
       </c>
-      <c r="D83" s="30" t="s">
+      <c r="D83" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E83" s="30" t="s">
+      <c r="E83" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="F83" s="29" t="s">
+      <c r="F83" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="G83" s="29" t="s">
+      <c r="G83" s="30" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="54" t="s">
+      <c r="A84" s="55" t="s">
         <v>223</v>
       </c>
-      <c r="B84" s="54" t="s">
+      <c r="B84" s="55" t="s">
         <v>224</v>
       </c>
-      <c r="C84" s="35" t="s">
+      <c r="C84" s="36" t="s">
         <v>225</v>
       </c>
-      <c r="D84" s="30" t="s">
+      <c r="D84" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E84" s="30" t="s">
+      <c r="E84" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="F84" s="29" t="s">
+      <c r="F84" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="G84" s="29" t="s">
+      <c r="G84" s="30" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="54" t="s">
+      <c r="A85" s="55" t="s">
         <v>227</v>
       </c>
-      <c r="B85" s="54" t="s">
+      <c r="B85" s="55" t="s">
         <v>227</v>
       </c>
-      <c r="C85" s="29" t="s">
+      <c r="C85" s="30" t="s">
         <v>228</v>
       </c>
-      <c r="D85" s="30" t="s">
+      <c r="D85" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E85" s="36" t="s">
+      <c r="E85" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="F85" s="29" t="s">
+      <c r="F85" s="30" t="s">
         <v>229</v>
       </c>
-      <c r="G85" s="29"/>
+      <c r="G85" s="30"/>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="54"/>
-      <c r="B86" s="54"/>
-      <c r="C86" s="29"/>
-      <c r="D86" s="30"/>
-      <c r="E86" s="30"/>
-      <c r="F86" s="29"/>
-      <c r="G86" s="29"/>
+      <c r="A86" s="55"/>
+      <c r="B86" s="55"/>
+      <c r="C86" s="30"/>
+      <c r="D86" s="31"/>
+      <c r="E86" s="31"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="30"/>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" s="54" t="s">
+      <c r="A87" s="55" t="s">
         <v>230</v>
       </c>
-      <c r="B87" s="54"/>
-      <c r="C87" s="29"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29"/>
+      <c r="B87" s="55"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="31"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
     </row>
     <row r="88" spans="1:7">
-      <c r="A88" s="54" t="s">
+      <c r="A88" s="55" t="s">
         <v>231</v>
       </c>
-      <c r="B88" s="54"/>
-      <c r="C88" s="29"/>
-      <c r="D88" s="30"/>
-      <c r="E88" s="30"/>
-      <c r="F88" s="29"/>
-      <c r="G88" s="29"/>
+      <c r="B88" s="55"/>
+      <c r="C88" s="30"/>
+      <c r="D88" s="31"/>
+      <c r="E88" s="31"/>
+      <c r="F88" s="30"/>
+      <c r="G88" s="30"/>
     </row>
     <row r="91" spans="1:7">
-      <c r="A91" s="54" t="s">
+      <c r="A91" s="55" t="s">
         <v>232</v>
       </c>
-      <c r="B91" s="54" t="s">
+      <c r="B91" s="55" t="s">
         <v>233</v>
       </c>
-      <c r="C91" s="29" t="s">
+      <c r="C91" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="D91" s="30" t="s">
+      <c r="D91" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E91" s="30" t="s">
+      <c r="E91" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="F91" s="29" t="s">
+      <c r="F91" s="30" t="s">
         <v>235</v>
       </c>
       <c r="G91" t="s">
@@ -4827,22 +4835,22 @@
       </c>
     </row>
     <row r="92" spans="1:7">
-      <c r="A92" s="54" t="s">
+      <c r="A92" s="55" t="s">
         <v>232</v>
       </c>
-      <c r="B92" s="54" t="s">
+      <c r="B92" s="55" t="s">
         <v>237</v>
       </c>
-      <c r="C92" s="29" t="s">
+      <c r="C92" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="D92" s="30" t="s">
+      <c r="D92" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E92" s="30" t="s">
+      <c r="E92" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="F92" s="29" t="s">
+      <c r="F92" s="30" t="s">
         <v>235</v>
       </c>
       <c r="G92" t="s">
@@ -4850,7 +4858,7 @@
       </c>
     </row>
     <row r="93" spans="1:7">
-      <c r="D93" s="26" t="s">
+      <c r="D93" s="27" t="s">
         <v>240</v>
       </c>
     </row>
@@ -4874,7 +4882,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="28.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="18.2685185185185" style="26" customWidth="1"/>
+    <col min="3" max="3" width="18.2685185185185" style="27" customWidth="1"/>
     <col min="4" max="4" width="17.0648148148148" customWidth="1"/>
     <col min="5" max="5" width="72" customWidth="1"/>
     <col min="6" max="6" width="23.462962962963" customWidth="1"/>
@@ -4882,1362 +4890,1362 @@
     <col min="8" max="8" width="31.6018518518519" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="24" customFormat="1" ht="28.5" customHeight="1" spans="1:7">
-      <c r="A1" s="27" t="s">
+    <row r="1" s="25" customFormat="1" ht="28.5" customHeight="1" spans="1:7">
+      <c r="A1" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>242</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="28" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="30" t="s">
         <v>245</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="30" t="s">
         <v>247</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-    </row>
-    <row r="6" s="25" customFormat="1" spans="1:7">
-      <c r="A6" s="31" t="s">
+      <c r="C5" s="31"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+    </row>
+    <row r="6" s="26" customFormat="1" spans="1:7">
+      <c r="A6" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31" t="s">
+      <c r="D6" s="32"/>
+      <c r="E6" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-    </row>
-    <row r="7" s="25" customFormat="1" spans="1:7">
-      <c r="A7" s="31" t="s">
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+    </row>
+    <row r="7" s="26" customFormat="1" spans="1:7">
+      <c r="A7" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31" t="s">
+      <c r="D7" s="32"/>
+      <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-    </row>
-    <row r="8" s="25" customFormat="1" spans="1:7">
-      <c r="A8" s="31" t="s">
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+    </row>
+    <row r="8" s="26" customFormat="1" spans="1:7">
+      <c r="A8" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31" t="s">
+      <c r="D8" s="32"/>
+      <c r="E8" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-    </row>
-    <row r="9" s="25" customFormat="1" spans="1:7">
-      <c r="A9" s="31" t="s">
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+    </row>
+    <row r="9" s="26" customFormat="1" spans="1:7">
+      <c r="A9" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31" t="s">
+      <c r="D9" s="32"/>
+      <c r="E9" s="32" t="s">
         <v>250</v>
       </c>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="36" t="s">
         <v>251</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35" t="s">
+      <c r="F10" s="36"/>
+      <c r="G10" s="36" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="30" t="s">
         <v>254</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="36" t="s">
         <v>255</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35" t="s">
+      <c r="D13" s="36"/>
+      <c r="E13" s="36" t="s">
         <v>256</v>
       </c>
-      <c r="F13" s="35"/>
-      <c r="G13" s="37" t="s">
+      <c r="F13" s="36"/>
+      <c r="G13" s="38" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35" t="s">
+      <c r="D14" s="36"/>
+      <c r="E14" s="36" t="s">
         <v>259</v>
       </c>
-      <c r="F14" s="35"/>
-      <c r="G14" s="37" t="s">
+      <c r="F14" s="36"/>
+      <c r="G14" s="38" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="30" t="s">
         <v>261</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34" t="s">
+      <c r="D17" s="35"/>
+      <c r="E17" s="35" t="s">
         <v>263</v>
       </c>
-      <c r="F17" s="35"/>
-      <c r="G17" s="37" t="s">
+      <c r="F17" s="36"/>
+      <c r="G17" s="38" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="29"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
+      <c r="A18" s="30"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31" t="s">
+      <c r="D19" s="32"/>
+      <c r="E19" s="32" t="s">
         <v>265</v>
       </c>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="34" t="s">
+      <c r="A20" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34" t="s">
+      <c r="D20" s="35"/>
+      <c r="E20" s="35" t="s">
         <v>266</v>
       </c>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35" t="s">
+      <c r="F20" s="36"/>
+      <c r="G20" s="36" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34" t="s">
+      <c r="D21" s="35"/>
+      <c r="E21" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35" t="s">
+      <c r="F21" s="36"/>
+      <c r="G21" s="36" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="B22" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35" t="s">
+      <c r="C22" s="37"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36" t="s">
         <v>270</v>
       </c>
-      <c r="F22" s="40" t="s">
+      <c r="F22" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="G22" s="35"/>
+      <c r="G22" s="36"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="35" t="s">
+      <c r="A23" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="35" t="s">
+      <c r="B23" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35" t="s">
+      <c r="C23" s="37"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36" t="s">
         <v>270</v>
       </c>
-      <c r="F23" s="41"/>
-      <c r="G23" s="35"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="36"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="37" t="s">
+      <c r="B24" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="C24" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34" t="s">
+      <c r="D24" s="35"/>
+      <c r="E24" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34" t="s">
+      <c r="D25" s="35"/>
+      <c r="E25" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="F25" s="35"/>
-      <c r="G25" s="37" t="s">
+      <c r="F25" s="36"/>
+      <c r="G25" s="38" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="30" t="s">
         <v>274</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C26" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29" t="s">
+      <c r="D26" s="30"/>
+      <c r="E26" s="30" t="s">
         <v>275</v>
       </c>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29" t="s">
+      <c r="F26" s="30"/>
+      <c r="G26" s="30" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31" t="s">
+      <c r="D27" s="32"/>
+      <c r="E27" s="32" t="s">
         <v>277</v>
       </c>
-      <c r="F27" s="35"/>
-      <c r="G27" s="37" t="s">
+      <c r="F27" s="36"/>
+      <c r="G27" s="38" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="C28" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34" t="s">
+      <c r="D28" s="35"/>
+      <c r="E28" s="35" t="s">
         <v>278</v>
       </c>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35" t="s">
+      <c r="F28" s="36"/>
+      <c r="G28" s="36" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="34" t="s">
+      <c r="A29" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="C29" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34" t="s">
+      <c r="D29" s="35"/>
+      <c r="E29" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="36"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="35" t="s">
+      <c r="A30" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="35" t="s">
+      <c r="B30" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="D30" s="35"/>
-      <c r="E30" s="35" t="s">
+      <c r="D30" s="36"/>
+      <c r="E30" s="36" t="s">
         <v>280</v>
       </c>
-      <c r="F30" s="42"/>
-      <c r="G30" s="37" t="s">
+      <c r="F30" s="43"/>
+      <c r="G30" s="38" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="C31" s="30"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="29"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="30"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="30" t="s">
         <v>282</v>
       </c>
-      <c r="C32" s="30"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="29"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="30"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="C33" s="30"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="29"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="30"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="30" t="s">
         <v>284</v>
       </c>
-      <c r="C34" s="30"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="29"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="30"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="29"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="29"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="30"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B36" s="29" t="s">
+      <c r="B36" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="C36" s="30"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="29"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="30"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="C37" s="30"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="29"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="30"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="29" t="s">
+      <c r="B38" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="C38" s="30"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="29"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="30"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="29" t="s">
+      <c r="A39" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="29" t="s">
+      <c r="B39" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="C39" s="30"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="29"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="30"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="35" t="s">
+      <c r="A40" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="35" t="s">
+      <c r="B40" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="C40" s="36"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="37" t="s">
+      <c r="C40" s="37"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="38" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="29" t="s">
+      <c r="A41" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="B41" s="29" t="s">
+      <c r="B41" s="30" t="s">
         <v>290</v>
       </c>
-      <c r="C41" s="30"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="29"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="30"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="29" t="s">
+      <c r="A42" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="B42" s="29" t="s">
+      <c r="B42" s="30" t="s">
         <v>291</v>
       </c>
-      <c r="C42" s="30"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="29"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="30"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="29" t="s">
+      <c r="A43" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="30" t="s">
         <v>292</v>
       </c>
-      <c r="C43" s="30"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="29"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="30"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="34" t="s">
+      <c r="A44" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="34" t="s">
+      <c r="B44" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="38" t="s">
+      <c r="C44" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34" t="s">
+      <c r="D44" s="35"/>
+      <c r="E44" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="F44" s="44"/>
-      <c r="G44" s="35" t="s">
+      <c r="F44" s="45"/>
+      <c r="G44" s="36" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="34" t="s">
+      <c r="A45" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="B45" s="34" t="s">
+      <c r="B45" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="C45" s="38" t="s">
+      <c r="C45" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34" t="s">
+      <c r="D45" s="35"/>
+      <c r="E45" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="F45" s="35"/>
-      <c r="G45" s="35"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="36"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="34" t="s">
+      <c r="A46" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="B46" s="34" t="s">
+      <c r="B46" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="C46" s="38" t="s">
+      <c r="C46" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="D46" s="34"/>
-      <c r="E46" s="34" t="s">
+      <c r="D46" s="35"/>
+      <c r="E46" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="F46" s="45" t="s">
+      <c r="F46" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="G46" s="35" t="s">
+      <c r="G46" s="36" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="47" ht="14.65" customHeight="1" spans="1:7">
-      <c r="A47" s="34" t="s">
+      <c r="A47" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="34" t="s">
+      <c r="B47" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="C47" s="38" t="s">
+      <c r="C47" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="D47" s="34"/>
-      <c r="E47" s="34" t="s">
+      <c r="D47" s="35"/>
+      <c r="E47" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="F47" s="46"/>
-      <c r="G47" s="35"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="36"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="35" t="s">
+      <c r="A48" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="B48" s="35" t="s">
+      <c r="B48" s="36" t="s">
         <v>297</v>
       </c>
-      <c r="C48" s="36" t="s">
+      <c r="C48" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="D48" s="35"/>
-      <c r="E48" s="35" t="s">
+      <c r="D48" s="36"/>
+      <c r="E48" s="36" t="s">
         <v>298</v>
       </c>
-      <c r="F48" s="35"/>
-      <c r="G48" s="37" t="s">
+      <c r="F48" s="36"/>
+      <c r="G48" s="38" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="35" t="s">
+      <c r="A49" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="B49" s="35" t="s">
+      <c r="B49" s="36" t="s">
         <v>300</v>
       </c>
-      <c r="C49" s="36" t="s">
+      <c r="C49" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="D49" s="35"/>
-      <c r="E49" s="35" t="s">
+      <c r="D49" s="36"/>
+      <c r="E49" s="36" t="s">
         <v>298</v>
       </c>
-      <c r="F49" s="35"/>
-      <c r="G49" s="37"/>
+      <c r="F49" s="36"/>
+      <c r="G49" s="38"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="35" t="s">
+      <c r="A50" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="B50" s="35" t="s">
+      <c r="B50" s="36" t="s">
         <v>301</v>
       </c>
-      <c r="C50" s="36" t="s">
+      <c r="C50" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="D50" s="35"/>
-      <c r="E50" s="35" t="s">
+      <c r="D50" s="36"/>
+      <c r="E50" s="36" t="s">
         <v>302</v>
       </c>
-      <c r="F50" s="35"/>
-      <c r="G50" s="37"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="38"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="35" t="s">
+      <c r="A51" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="B51" s="35" t="s">
+      <c r="B51" s="36" t="s">
         <v>303</v>
       </c>
-      <c r="C51" s="36" t="s">
+      <c r="C51" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="D51" s="35"/>
-      <c r="E51" s="35" t="s">
+      <c r="D51" s="36"/>
+      <c r="E51" s="36" t="s">
         <v>304</v>
       </c>
-      <c r="F51" s="35"/>
-      <c r="G51" s="37"/>
+      <c r="F51" s="36"/>
+      <c r="G51" s="38"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="29"/>
-      <c r="B52" s="29"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
+      <c r="A52" s="30"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="29" t="s">
+      <c r="A53" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="B53" s="29" t="s">
+      <c r="B53" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="C53" s="30"/>
-      <c r="D53" s="29"/>
-      <c r="E53" s="29"/>
-      <c r="F53" s="29"/>
-      <c r="G53" s="29"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="29" t="s">
+      <c r="A54" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="B54" s="29" t="s">
+      <c r="B54" s="30" t="s">
         <v>306</v>
       </c>
-      <c r="C54" s="30"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="29"/>
-      <c r="F54" s="29"/>
-      <c r="G54" s="29"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="29" t="s">
+      <c r="A55" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="B55" s="29" t="s">
+      <c r="B55" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="C55" s="30"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="B56" s="29" t="s">
+      <c r="B56" s="30" t="s">
         <v>308</v>
       </c>
-      <c r="C56" s="30"/>
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="29"/>
+      <c r="C56" s="31"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="34" t="s">
+      <c r="A57" s="35" t="s">
         <v>149</v>
       </c>
-      <c r="B57" s="34" t="s">
+      <c r="B57" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="C57" s="38" t="s">
+      <c r="C57" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="D57" s="34"/>
-      <c r="E57" s="34" t="s">
+      <c r="D57" s="35"/>
+      <c r="E57" s="35" t="s">
         <v>309</v>
       </c>
-      <c r="F57" s="35"/>
-      <c r="G57" s="35" t="s">
+      <c r="F57" s="36"/>
+      <c r="G57" s="36" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="B58" s="29" t="s">
+      <c r="B58" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="C58" s="30"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="29" t="s">
+      <c r="A59" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="B59" s="29" t="s">
+      <c r="B59" s="30" t="s">
         <v>312</v>
       </c>
-      <c r="C59" s="30"/>
-      <c r="D59" s="29"/>
-      <c r="E59" s="29"/>
-      <c r="F59" s="29"/>
-      <c r="G59" s="29"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="29" t="s">
+      <c r="A60" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="B60" s="29" t="s">
+      <c r="B60" s="30" t="s">
         <v>313</v>
       </c>
-      <c r="C60" s="30"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
-      <c r="F60" s="29"/>
-      <c r="G60" s="29"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="37" t="s">
+      <c r="A61" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="B61" s="37" t="s">
+      <c r="B61" s="38" t="s">
         <v>314</v>
       </c>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="47" t="s">
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="48" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="37" t="s">
+      <c r="A62" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="B62" s="37" t="s">
+      <c r="B62" s="38" t="s">
         <v>316</v>
       </c>
-      <c r="C62" s="30"/>
-      <c r="D62" s="29"/>
-      <c r="E62" s="29"/>
-      <c r="F62" s="29"/>
-      <c r="G62" s="48"/>
+      <c r="C62" s="31"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="49"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="29" t="s">
+      <c r="A63" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="29" t="s">
+      <c r="B63" s="30" t="s">
         <v>317</v>
       </c>
-      <c r="C63" s="30"/>
-      <c r="D63" s="29"/>
-      <c r="E63" s="29"/>
-      <c r="F63" s="29"/>
-      <c r="G63" s="29"/>
+      <c r="C63" s="31"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="29" t="s">
+      <c r="A64" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="B64" s="29" t="s">
+      <c r="B64" s="30" t="s">
         <v>318</v>
       </c>
-      <c r="C64" s="30"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="35" t="s">
+      <c r="A65" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="B65" s="35" t="s">
+      <c r="B65" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="C65" s="36" t="s">
+      <c r="C65" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="D65" s="35"/>
-      <c r="E65" s="35" t="s">
+      <c r="D65" s="36"/>
+      <c r="E65" s="36" t="s">
         <v>319</v>
       </c>
-      <c r="F65" s="35"/>
-      <c r="G65" s="37" t="s">
+      <c r="F65" s="36"/>
+      <c r="G65" s="38" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="29" t="s">
+      <c r="A66" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="29" t="s">
+      <c r="B66" s="30" t="s">
         <v>320</v>
       </c>
-      <c r="C66" s="30"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="29"/>
-      <c r="G66" s="29"/>
+      <c r="C66" s="31"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="34" t="s">
+      <c r="A67" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="B67" s="34" t="s">
+      <c r="B67" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="C67" s="38" t="s">
+      <c r="C67" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D67" s="34"/>
-      <c r="E67" s="34" t="s">
+      <c r="D67" s="35"/>
+      <c r="E67" s="35" t="s">
         <v>321</v>
       </c>
-      <c r="F67" s="35" t="s">
+      <c r="F67" s="36" t="s">
         <v>322</v>
       </c>
-      <c r="G67" s="35" t="s">
+      <c r="G67" s="36" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="34" t="s">
+      <c r="A68" s="35" t="s">
         <v>159</v>
       </c>
-      <c r="B68" s="34" t="s">
+      <c r="B68" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="C68" s="38" t="s">
+      <c r="C68" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D68" s="34"/>
-      <c r="E68" s="34" t="s">
+      <c r="D68" s="35"/>
+      <c r="E68" s="35" t="s">
         <v>321</v>
       </c>
-      <c r="F68" s="35" t="s">
+      <c r="F68" s="36" t="s">
         <v>322</v>
       </c>
-      <c r="G68" s="35" t="s">
+      <c r="G68" s="36" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="29"/>
-      <c r="B69" s="29"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
+      <c r="A69" s="30"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="34" t="s">
+      <c r="A70" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="B70" s="34" t="s">
+      <c r="B70" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="C70" s="38"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="34" t="s">
+      <c r="C70" s="39"/>
+      <c r="D70" s="35"/>
+      <c r="E70" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="F70" s="35"/>
-      <c r="G70" s="37" t="s">
+      <c r="F70" s="36"/>
+      <c r="G70" s="38" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="34" t="s">
+      <c r="A71" s="35" t="s">
         <v>182</v>
       </c>
-      <c r="B71" s="34" t="s">
+      <c r="B71" s="35" t="s">
         <v>184</v>
       </c>
-      <c r="C71" s="38"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34" t="s">
+      <c r="C71" s="39"/>
+      <c r="D71" s="35"/>
+      <c r="E71" s="35" t="s">
         <v>326</v>
       </c>
-      <c r="F71" s="35"/>
-      <c r="G71" s="37" t="s">
+      <c r="F71" s="36"/>
+      <c r="G71" s="38" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="34" t="s">
+      <c r="A72" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="B72" s="34" t="s">
+      <c r="B72" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="C72" s="38" t="s">
+      <c r="C72" s="39" t="s">
         <v>242</v>
       </c>
-      <c r="D72" s="34"/>
-      <c r="E72" s="34" t="s">
+      <c r="D72" s="35"/>
+      <c r="E72" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="F72" s="35"/>
-      <c r="G72" s="35"/>
+      <c r="F72" s="36"/>
+      <c r="G72" s="36"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="34" t="s">
+      <c r="A73" s="35" t="s">
         <v>189</v>
       </c>
-      <c r="B73" s="34" t="s">
+      <c r="B73" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="C73" s="38" t="s">
+      <c r="C73" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="D73" s="34"/>
-      <c r="E73" s="34" t="s">
+      <c r="D73" s="35"/>
+      <c r="E73" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="F73" s="35"/>
-      <c r="G73" s="35"/>
+      <c r="F73" s="36"/>
+      <c r="G73" s="36"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="35" t="s">
+      <c r="A74" s="36" t="s">
         <v>191</v>
       </c>
-      <c r="B74" s="35" t="s">
+      <c r="B74" s="36" t="s">
         <v>328</v>
       </c>
-      <c r="C74" s="36" t="s">
+      <c r="C74" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="D74" s="35"/>
-      <c r="E74" s="35" t="s">
+      <c r="D74" s="36"/>
+      <c r="E74" s="36" t="s">
         <v>329</v>
       </c>
-      <c r="F74" s="35"/>
-      <c r="G74" s="37" t="s">
+      <c r="F74" s="36"/>
+      <c r="G74" s="38" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="35" t="s">
+      <c r="A75" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="B75" s="35" t="s">
+      <c r="B75" s="36" t="s">
         <v>331</v>
       </c>
-      <c r="C75" s="36" t="s">
+      <c r="C75" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35" t="s">
+      <c r="D75" s="36"/>
+      <c r="E75" s="36" t="s">
         <v>332</v>
       </c>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
+      <c r="F75" s="36"/>
+      <c r="G75" s="36"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="35" t="s">
+      <c r="A76" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="B76" s="35" t="s">
+      <c r="B76" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="C76" s="36" t="s">
+      <c r="C76" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35" t="s">
+      <c r="D76" s="36"/>
+      <c r="E76" s="36" t="s">
         <v>333</v>
       </c>
-      <c r="F76" s="35"/>
-      <c r="G76" s="37" t="s">
+      <c r="F76" s="36"/>
+      <c r="G76" s="38" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="35" t="s">
+      <c r="A77" s="36" t="s">
         <v>200</v>
       </c>
-      <c r="B77" s="35" t="s">
+      <c r="B77" s="36" t="s">
         <v>201</v>
       </c>
-      <c r="C77" s="36"/>
-      <c r="D77" s="35"/>
-      <c r="E77" s="35"/>
-      <c r="F77" s="35"/>
-      <c r="G77" s="37" t="s">
+      <c r="C77" s="37"/>
+      <c r="D77" s="36"/>
+      <c r="E77" s="36"/>
+      <c r="F77" s="36"/>
+      <c r="G77" s="38" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="35" t="s">
+      <c r="A78" s="36" t="s">
         <v>203</v>
       </c>
-      <c r="B78" s="35" t="s">
+      <c r="B78" s="36" t="s">
         <v>204</v>
       </c>
-      <c r="C78" s="36"/>
-      <c r="D78" s="35"/>
-      <c r="E78" s="35"/>
-      <c r="F78" s="35"/>
-      <c r="G78" s="37" t="s">
+      <c r="C78" s="37"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+      <c r="G78" s="38" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="35" t="s">
+      <c r="A79" s="36" t="s">
         <v>206</v>
       </c>
-      <c r="B79" s="35" t="s">
+      <c r="B79" s="36" t="s">
         <v>335</v>
       </c>
-      <c r="C79" s="36" t="s">
+      <c r="C79" s="37" t="s">
         <v>249</v>
       </c>
-      <c r="D79" s="35"/>
-      <c r="E79" s="35" t="s">
+      <c r="D79" s="36"/>
+      <c r="E79" s="36" t="s">
         <v>336</v>
       </c>
-      <c r="F79" s="35"/>
-      <c r="G79" s="37" t="s">
+      <c r="F79" s="36"/>
+      <c r="G79" s="38" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="29" t="s">
+      <c r="A80" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="B80" s="29" t="s">
+      <c r="B80" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="C80" s="30"/>
-      <c r="D80" s="29"/>
-      <c r="E80" s="29"/>
-      <c r="F80" s="29"/>
-      <c r="G80" s="29" t="s">
+      <c r="C80" s="31"/>
+      <c r="D80" s="30"/>
+      <c r="E80" s="30"/>
+      <c r="F80" s="30"/>
+      <c r="G80" s="30" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" s="34" t="s">
+      <c r="A81" s="35" t="s">
         <v>210</v>
       </c>
-      <c r="B81" s="34" t="s">
+      <c r="B81" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="C81" s="38" t="s">
+      <c r="C81" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D81" s="34"/>
-      <c r="E81" s="34" t="s">
+      <c r="D81" s="35"/>
+      <c r="E81" s="35" t="s">
         <v>338</v>
       </c>
-      <c r="F81" s="34"/>
-      <c r="G81" s="37" t="s">
+      <c r="F81" s="35"/>
+      <c r="G81" s="38" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="82" spans="1:7">
-      <c r="A82" s="29" t="s">
+      <c r="A82" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="B82" s="29" t="s">
+      <c r="B82" s="30" t="s">
         <v>339</v>
       </c>
-      <c r="C82" s="30"/>
-      <c r="D82" s="29"/>
-      <c r="E82" s="29"/>
-      <c r="F82" s="29"/>
-      <c r="G82" s="29"/>
+      <c r="C82" s="31"/>
+      <c r="D82" s="30"/>
+      <c r="E82" s="30"/>
+      <c r="F82" s="30"/>
+      <c r="G82" s="30"/>
     </row>
     <row r="83" spans="1:7">
-      <c r="A83" s="29" t="s">
+      <c r="A83" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="B83" s="29" t="s">
+      <c r="B83" s="30" t="s">
         <v>340</v>
       </c>
-      <c r="C83" s="30"/>
-      <c r="D83" s="29"/>
-      <c r="E83" s="29"/>
-      <c r="F83" s="29"/>
-      <c r="G83" s="29"/>
+      <c r="C83" s="31"/>
+      <c r="D83" s="30"/>
+      <c r="E83" s="30"/>
+      <c r="F83" s="30"/>
+      <c r="G83" s="30"/>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="29" t="s">
+      <c r="A84" s="30" t="s">
         <v>223</v>
       </c>
-      <c r="B84" s="29" t="s">
+      <c r="B84" s="30" t="s">
         <v>341</v>
       </c>
-      <c r="C84" s="30"/>
-      <c r="D84" s="29"/>
-      <c r="E84" s="29"/>
-      <c r="F84" s="29"/>
-      <c r="G84" s="29"/>
+      <c r="C84" s="31"/>
+      <c r="D84" s="30"/>
+      <c r="E84" s="30"/>
+      <c r="F84" s="30"/>
+      <c r="G84" s="30"/>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="29" t="s">
+      <c r="A85" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="B85" s="29" t="s">
+      <c r="B85" s="30" t="s">
         <v>342</v>
       </c>
-      <c r="C85" s="30"/>
-      <c r="D85" s="29"/>
-      <c r="E85" s="29"/>
-      <c r="F85" s="29"/>
-      <c r="G85" s="29"/>
+      <c r="C85" s="31"/>
+      <c r="D85" s="30"/>
+      <c r="E85" s="30"/>
+      <c r="F85" s="30"/>
+      <c r="G85" s="30"/>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="29"/>
-      <c r="B86" s="29"/>
-      <c r="C86" s="30"/>
-      <c r="D86" s="29"/>
-      <c r="E86" s="29"/>
-      <c r="F86" s="29"/>
-      <c r="G86" s="29"/>
+      <c r="A86" s="30"/>
+      <c r="B86" s="30"/>
+      <c r="C86" s="31"/>
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="30"/>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" s="29" t="s">
+      <c r="A87" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="B87" s="29" t="s">
+      <c r="B87" s="30" t="s">
         <v>343</v>
       </c>
-      <c r="C87" s="30"/>
-      <c r="D87" s="29"/>
-      <c r="E87" s="29"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29"/>
+      <c r="C87" s="31"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
     </row>
     <row r="88" spans="1:7">
-      <c r="A88" s="29" t="s">
+      <c r="A88" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="B88" s="29" t="s">
+      <c r="B88" s="30" t="s">
         <v>344</v>
       </c>
-      <c r="C88" s="30"/>
-      <c r="D88" s="29"/>
-      <c r="E88" s="29"/>
-      <c r="F88" s="29"/>
-      <c r="G88" s="29"/>
+      <c r="C88" s="31"/>
+      <c r="D88" s="30"/>
+      <c r="E88" s="30"/>
+      <c r="F88" s="30"/>
+      <c r="G88" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6821,12 +6829,10 @@
       <c r="F24" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="18" t="s">
         <v>415</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>361</v>
-      </c>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="11">
@@ -6847,12 +6853,10 @@
       <c r="F25" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="G25" s="18" t="s">
         <v>418</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>361</v>
-      </c>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="11">
@@ -6921,7 +6925,7 @@
       <c r="F28" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G28" s="18" t="s">
+      <c r="G28" s="19" t="s">
         <v>427</v>
       </c>
       <c r="H28" s="11"/>
@@ -6943,7 +6947,7 @@
         <v>354</v>
       </c>
       <c r="F29" s="3"/>
-      <c r="G29" s="18"/>
+      <c r="G29" s="19"/>
       <c r="H29" s="11"/>
     </row>
     <row r="30" spans="1:8">
@@ -6965,7 +6969,7 @@
       <c r="F30" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G30" s="18" t="s">
+      <c r="G30" s="19" t="s">
         <v>432</v>
       </c>
       <c r="H30" s="15" t="s">
@@ -6989,7 +6993,7 @@
         <v>354</v>
       </c>
       <c r="F31" s="3"/>
-      <c r="G31" s="18"/>
+      <c r="G31" s="19"/>
       <c r="H31" s="17"/>
     </row>
     <row r="32" spans="1:8">
@@ -7323,13 +7327,13 @@
       <c r="D46" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="E46" s="20" t="s">
         <v>364</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G46" s="20" t="s">
+      <c r="G46" s="21" t="s">
         <v>371</v>
       </c>
       <c r="H46" s="4"/>
@@ -7379,7 +7383,7 @@
       <c r="F48" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="G48" s="21" t="s">
+      <c r="G48" s="22" t="s">
         <v>478</v>
       </c>
       <c r="H48" s="11"/>
@@ -7401,7 +7405,7 @@
         <v>364</v>
       </c>
       <c r="F49" s="17"/>
-      <c r="G49" s="22"/>
+      <c r="G49" s="23"/>
       <c r="H49" s="11"/>
     </row>
     <row r="50" spans="1:8">
@@ -7423,7 +7427,7 @@
       <c r="F50" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="G50" s="21" t="s">
+      <c r="G50" s="22" t="s">
         <v>483</v>
       </c>
       <c r="H50" s="11"/>
@@ -7445,7 +7449,7 @@
         <v>364</v>
       </c>
       <c r="F51" s="17"/>
-      <c r="G51" s="22"/>
+      <c r="G51" s="23"/>
       <c r="H51" s="11"/>
     </row>
     <row r="52" spans="1:8">
@@ -7465,10 +7469,10 @@
       <c r="B53" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="C53" s="23" t="s">
+      <c r="C53" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D53" s="23" t="s">
+      <c r="D53" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E53" s="11"/>
@@ -7483,10 +7487,10 @@
       <c r="B54" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="C54" s="23" t="s">
+      <c r="C54" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D54" s="23" t="s">
+      <c r="D54" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E54" s="11"/>
@@ -7501,10 +7505,10 @@
       <c r="B55" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="C55" s="23" t="s">
+      <c r="C55" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D55" s="23" t="s">
+      <c r="D55" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E55" s="11"/>
@@ -7519,10 +7523,10 @@
       <c r="B56" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D56" s="23" t="s">
+      <c r="D56" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E56" s="11"/>
@@ -7537,10 +7541,10 @@
       <c r="B57" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D57" s="23" t="s">
+      <c r="D57" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E57" s="11"/>
@@ -7555,10 +7559,10 @@
       <c r="B58" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D58" s="23" t="s">
+      <c r="D58" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E58" s="11"/>
@@ -7573,10 +7577,10 @@
       <c r="B59" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="C59" s="23" t="s">
+      <c r="C59" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D59" s="23" t="s">
+      <c r="D59" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E59" s="11"/>
@@ -7591,10 +7595,10 @@
       <c r="B60" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D60" s="23" t="s">
+      <c r="D60" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E60" s="11"/>
@@ -7609,10 +7613,10 @@
       <c r="B61" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D61" s="23" t="s">
+      <c r="D61" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E61" s="11"/>
@@ -7627,10 +7631,10 @@
       <c r="B62" s="11" t="s">
         <v>494</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D62" s="23" t="s">
+      <c r="D62" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E62" s="11"/>
@@ -7645,10 +7649,10 @@
       <c r="B63" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D63" s="23" t="s">
+      <c r="D63" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E63" s="11"/>
@@ -7663,10 +7667,10 @@
       <c r="B64" s="11" t="s">
         <v>496</v>
       </c>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D64" s="23" t="s">
+      <c r="D64" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E64" s="11"/>
@@ -7681,10 +7685,10 @@
       <c r="B65" s="11" t="s">
         <v>497</v>
       </c>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D65" s="23" t="s">
+      <c r="D65" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E65" s="11"/>
@@ -7699,10 +7703,10 @@
       <c r="B66" s="11" t="s">
         <v>498</v>
       </c>
-      <c r="C66" s="23" t="s">
+      <c r="C66" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D66" s="23" t="s">
+      <c r="D66" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E66" s="11"/>
@@ -7717,10 +7721,10 @@
       <c r="B67" s="11" t="s">
         <v>499</v>
       </c>
-      <c r="C67" s="23" t="s">
+      <c r="C67" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D67" s="23" t="s">
+      <c r="D67" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E67" s="11"/>
@@ -7735,7 +7739,7 @@
       <c r="B68" s="11" t="s">
         <v>500</v>
       </c>
-      <c r="C68" s="23" t="s">
+      <c r="C68" s="24" t="s">
         <v>409</v>
       </c>
       <c r="D68" s="11" t="s">
@@ -7759,10 +7763,10 @@
       <c r="B69" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="C69" s="23" t="s">
+      <c r="C69" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D69" s="23" t="s">
+      <c r="D69" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E69" s="11"/>
@@ -7777,10 +7781,10 @@
       <c r="B70" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="C70" s="23" t="s">
+      <c r="C70" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="D70" s="23" t="s">
+      <c r="D70" s="24" t="s">
         <v>409</v>
       </c>
       <c r="E70" s="11"/>

--- a/BPCOME-3502单片机需求260724a.xlsx
+++ b/BPCOME-3502单片机需求260724a.xlsx
@@ -1351,7 +1351,7 @@
     <t>PWRBTN_OUT#</t>
   </si>
   <si>
-    <t>做输出给核心卡，当接收到PB4有20ms低电平或以上，就输出20ms低电平脉冲</t>
+    <t>做输出给核心卡，当接收到PB4有20ms低电平或以上，就输出200ms低电平脉冲</t>
   </si>
   <si>
     <t xml:space="preserve">PB6 </t>

--- a/BPCOME-3502单片机需求260724a.xlsx
+++ b/BPCOME-3502单片机需求260724a.xlsx
@@ -1228,7 +1228,7 @@
     <t>CB_RESET#</t>
   </si>
   <si>
-    <t>做输入，核心卡复位输出信号</t>
+    <t>做输入，核心卡复位输出信号 （浮空）</t>
   </si>
   <si>
     <t>12V电压采集，系数12</t>
@@ -1297,7 +1297,7 @@
     <t>PWRSUS_EN</t>
   </si>
   <si>
-    <t>预留，输出，SUS电源使能高有效</t>
+    <t>预留，输出，SUS电源使能高有效  更改成参考PC0</t>
   </si>
   <si>
     <t xml:space="preserve">PB0 </t>
@@ -1333,7 +1333,7 @@
     <t>PWREN</t>
   </si>
   <si>
-    <t>预留，输出，S0域电源使能高有效</t>
+    <t>预留，输出，S0域电源使能高有效 （浮空）</t>
   </si>
   <si>
     <t xml:space="preserve">PB4 </t>
@@ -1360,7 +1360,7 @@
     <t>P3V3SUS_PG</t>
   </si>
   <si>
-    <t>做输入，P3V3SUS电源PG信号</t>
+    <t>做输入，P3V3SUS电源PG信号 （浮空）</t>
   </si>
   <si>
     <t xml:space="preserve">PB7 </t>
@@ -1369,7 +1369,7 @@
     <t>P3V3_STBY_PG</t>
   </si>
   <si>
-    <t>做输入，P3V3_STBY电源PG信号</t>
+    <t>做输入，P3V3_STBY电源PG信号 （浮空）</t>
   </si>
   <si>
     <t xml:space="preserve">PB8 </t>
@@ -1417,7 +1417,8 @@
     <t>PWROK</t>
   </si>
   <si>
-    <t xml:space="preserve">底板电源OK信号输出，参考PB6高后输出高  </t>
+    <t>底板电源OK信号输出，参考PB6高后输出高  改成底板电源OK信号输出，不操作一直
+保持低电平  改成底板电源OK信号输出，参考PC0</t>
   </si>
   <si>
     <t xml:space="preserve">PB14 </t>
@@ -1444,7 +1445,7 @@
     <t>SLP_S3#</t>
   </si>
   <si>
-    <t>核心卡S3睡眠信号输入，低有效  改成了自检，高表示开机低表示关机</t>
+    <t>核心卡S3睡眠信号输入，低有效  改成了自检，高表示开机低表示关机（浮空）</t>
   </si>
   <si>
     <t xml:space="preserve">PC1 </t>
@@ -1453,7 +1454,7 @@
     <t>SLP_S4#</t>
   </si>
   <si>
-    <t>核心卡S4休眠信号输入，低有效</t>
+    <t>核心卡S4休眠信号输入，低有效（浮空）</t>
   </si>
   <si>
     <t xml:space="preserve">PC2 </t>
@@ -1462,7 +1463,7 @@
     <t>SLP_S5#</t>
   </si>
   <si>
-    <t>核心卡S5关机信号输入，低有效</t>
+    <t>核心卡S5关机信号输入，低有效（浮空）</t>
   </si>
   <si>
     <t xml:space="preserve">PC3 </t>
@@ -2341,7 +2342,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2393,6 +2394,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3205,1629 +3209,1629 @@
   <dimension ref="A1:G93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="12.3333333333333" style="51" customWidth="1"/>
-    <col min="2" max="2" width="13" style="51" customWidth="1"/>
+    <col min="1" max="1" width="12.3333333333333" style="52" customWidth="1"/>
+    <col min="2" max="2" width="13" style="52" customWidth="1"/>
     <col min="3" max="3" width="23.7314814814815" customWidth="1"/>
-    <col min="4" max="4" width="9.73148148148148" style="27" customWidth="1"/>
-    <col min="5" max="5" width="10.7314814814815" style="27" customWidth="1"/>
+    <col min="4" max="4" width="9.73148148148148" style="28" customWidth="1"/>
+    <col min="5" max="5" width="10.7314814814815" style="28" customWidth="1"/>
     <col min="6" max="6" width="70" customWidth="1"/>
     <col min="7" max="7" width="95.6018518518518" customWidth="1"/>
     <col min="8" max="8" width="31.6018518518519" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="50" customFormat="1" ht="22.2" spans="1:7">
-      <c r="A1" s="52" t="s">
+    <row r="1" s="51" customFormat="1" ht="22.2" spans="1:7">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="53" t="s">
+      <c r="F1" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="53" t="s">
+      <c r="G1" s="54" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="37" t="s">
+      <c r="D2" s="32"/>
+      <c r="E2" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="37" t="s">
+      <c r="D3" s="32"/>
+      <c r="E3" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="37" t="s">
+      <c r="D4" s="32"/>
+      <c r="E4" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="37" t="s">
+      <c r="D5" s="32"/>
+      <c r="E5" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="55" t="s">
+      <c r="B6" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="30"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="30"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="30"/>
+      <c r="G8" s="31"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="F9" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="30"/>
+      <c r="G9" s="31"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="55" t="s">
+      <c r="B10" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="30"/>
+      <c r="G10" s="31"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="55" t="s">
+      <c r="B11" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="F11" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="30"/>
+      <c r="G11" s="31"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="30"/>
+      <c r="G12" s="31"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="55"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="55"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="55" t="s">
+      <c r="B15" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="55" t="s">
+      <c r="B16" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="55" t="s">
+      <c r="A17" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="C17" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="30" t="s">
+      <c r="F17" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="30"/>
+      <c r="G17" s="31"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="55"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
+      <c r="A18" s="56"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="55" t="s">
+      <c r="A19" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="30" t="s">
+      <c r="F19" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="G19" s="30"/>
+      <c r="G19" s="31"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="55" t="s">
+      <c r="A20" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="55" t="s">
+      <c r="B20" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="44" t="s">
+      <c r="C20" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="37" t="s">
+      <c r="D20" s="32"/>
+      <c r="E20" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="55" t="s">
+      <c r="B21" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="31" t="s">
+      <c r="D21" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="30" t="s">
+      <c r="F21" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="30"/>
+      <c r="G21" s="31"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="55" t="s">
+      <c r="B22" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D22" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="31" t="s">
+      <c r="E22" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="30" t="s">
+      <c r="F22" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="G22" s="30"/>
+      <c r="G22" s="31"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="55" t="s">
+      <c r="B23" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C23" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="D23" s="31" t="s">
+      <c r="D23" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="31" t="s">
+      <c r="E23" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="30" t="s">
+      <c r="F23" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="G23" s="30"/>
+      <c r="G23" s="31"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="55" t="s">
+      <c r="A24" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="55" t="s">
+      <c r="B24" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="E24" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="30" t="s">
+      <c r="F24" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="G24" s="30"/>
+      <c r="G24" s="31"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="55" t="s">
+      <c r="A25" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C25" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="31" t="s">
+      <c r="D25" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="31" t="s">
+      <c r="E25" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="G25" s="30"/>
+      <c r="G25" s="31"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="55" t="s">
+      <c r="A26" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="55" t="s">
+      <c r="B26" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C26" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D26" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E26" s="31" t="s">
+      <c r="E26" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="G26" s="30"/>
+      <c r="G26" s="31"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="55" t="s">
+      <c r="A27" s="56" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="55" t="s">
+      <c r="B27" s="56" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="C27" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="D27" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E27" s="31" t="s">
+      <c r="E27" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="F27" s="30" t="s">
+      <c r="F27" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="G27" s="30"/>
+      <c r="G27" s="31"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="55" t="s">
+      <c r="A28" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="55" t="s">
+      <c r="B28" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="C28" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="31" t="s">
+      <c r="D28" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E28" s="31" t="s">
+      <c r="E28" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="F28" s="30" t="s">
+      <c r="F28" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="G28" s="30"/>
+      <c r="G28" s="31"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="55" t="s">
+      <c r="A29" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="C29" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="D29" s="31" t="s">
+      <c r="D29" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="31" t="s">
+      <c r="E29" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="30" t="s">
+      <c r="F29" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="G29" s="30"/>
+      <c r="G29" s="31"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="55" t="s">
+      <c r="A30" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="55" t="s">
+      <c r="B30" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C30" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="31" t="s">
+      <c r="D30" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="31" t="s">
+      <c r="E30" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F30" s="30" t="s">
+      <c r="F30" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="G30" s="30"/>
+      <c r="G30" s="31"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="55" t="s">
+      <c r="A31" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="56" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="30" t="s">
+      <c r="C31" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="31" t="s">
+      <c r="D31" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="37" t="s">
+      <c r="E31" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F31" s="30" t="s">
+      <c r="F31" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="G31" s="30"/>
+      <c r="G31" s="31"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="55" t="s">
+      <c r="A32" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="55" t="s">
+      <c r="B32" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="31" t="s">
+      <c r="D32" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="37" t="s">
+      <c r="E32" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F32" s="30" t="s">
+      <c r="F32" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="G32" s="30"/>
+      <c r="G32" s="31"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="55" t="s">
+      <c r="B33" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="30" t="s">
+      <c r="C33" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="31" t="s">
+      <c r="D33" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E33" s="37" t="s">
+      <c r="E33" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F33" s="30" t="s">
+      <c r="F33" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="G33" s="30"/>
+      <c r="G33" s="31"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="55" t="s">
+      <c r="A34" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="55"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="55"/>
-      <c r="B35" s="55"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="55" t="s">
+      <c r="A36" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="B36" s="55" t="s">
+      <c r="B36" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="C36" s="30" t="s">
+      <c r="C36" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="D36" s="31"/>
-      <c r="E36" s="37" t="s">
+      <c r="D36" s="32"/>
+      <c r="E36" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="55" t="s">
+      <c r="A37" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="55" t="s">
+      <c r="B37" s="56" t="s">
         <v>109</v>
       </c>
-      <c r="C37" s="30" t="s">
+      <c r="C37" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="31"/>
-      <c r="E37" s="37" t="s">
+      <c r="D37" s="32"/>
+      <c r="E37" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="55" t="s">
+      <c r="A38" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="55" t="s">
+      <c r="B38" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C38" s="30" t="s">
+      <c r="C38" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="D38" s="31"/>
-      <c r="E38" s="37" t="s">
+      <c r="D38" s="32"/>
+      <c r="E38" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="55" t="s">
+      <c r="A39" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="55" t="s">
+      <c r="B39" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="56" t="s">
+      <c r="C39" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="D39" s="31" t="s">
+      <c r="D39" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E39" s="37" t="s">
+      <c r="E39" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F39" s="38" t="s">
+      <c r="F39" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="G39" s="30"/>
+      <c r="G39" s="31"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="55" t="s">
+      <c r="A40" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="55" t="s">
+      <c r="B40" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="C40" s="30" t="s">
+      <c r="C40" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="D40" s="31"/>
-      <c r="E40" s="37" t="s">
+      <c r="D40" s="32"/>
+      <c r="E40" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="55" t="s">
+      <c r="A41" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="B41" s="55" t="s">
+      <c r="B41" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="C41" s="30" t="s">
+      <c r="C41" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="D41" s="31"/>
-      <c r="E41" s="37" t="s">
+      <c r="D41" s="32"/>
+      <c r="E41" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="55" t="s">
+      <c r="A42" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="B42" s="55"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="57"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="30"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="31"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="55" t="s">
+      <c r="A43" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="B43" s="55"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="55" t="s">
+      <c r="A44" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="55" t="s">
+      <c r="B44" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="30" t="s">
+      <c r="C44" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="D44" s="31" t="s">
+      <c r="D44" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E44" s="31" t="s">
+      <c r="E44" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F44" s="30" t="s">
+      <c r="F44" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="G44" s="30"/>
+      <c r="G44" s="31"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="55" t="s">
+      <c r="A45" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="B45" s="55" t="s">
+      <c r="B45" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="C45" s="30" t="s">
+      <c r="C45" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="D45" s="31" t="s">
+      <c r="D45" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E45" s="31" t="s">
+      <c r="E45" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F45" s="30" t="s">
+      <c r="F45" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="G45" s="30"/>
+      <c r="G45" s="31"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="55" t="s">
+      <c r="A46" s="56" t="s">
         <v>126</v>
       </c>
-      <c r="B46" s="55" t="s">
+      <c r="B46" s="56" t="s">
         <v>127</v>
       </c>
-      <c r="C46" s="30" t="s">
+      <c r="C46" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="D46" s="31" t="s">
+      <c r="D46" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="E46" s="31" t="s">
+      <c r="E46" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="F46" s="30" t="s">
+      <c r="F46" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="G46" s="30"/>
+      <c r="G46" s="31"/>
     </row>
     <row r="47" ht="14.65" customHeight="1" spans="1:7">
-      <c r="A47" s="55" t="s">
+      <c r="A47" s="56" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="55" t="s">
+      <c r="B47" s="56" t="s">
         <v>131</v>
       </c>
-      <c r="C47" s="30" t="s">
+      <c r="C47" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="D47" s="31" t="s">
+      <c r="D47" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="E47" s="31" t="s">
+      <c r="E47" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="30" t="s">
+      <c r="F47" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="G47" s="30"/>
+      <c r="G47" s="31"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="55" t="s">
+      <c r="A48" s="56" t="s">
         <v>134</v>
       </c>
-      <c r="B48" s="55"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
+      <c r="B48" s="56"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="55" t="s">
+      <c r="A49" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="B49" s="55"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
+      <c r="B49" s="56"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="55" t="s">
+      <c r="A50" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="B50" s="55"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="30"/>
+      <c r="B50" s="56"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="31"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="55" t="s">
+      <c r="A51" s="56" t="s">
         <v>137</v>
       </c>
-      <c r="B51" s="55"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="30"/>
+      <c r="B51" s="56"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="55"/>
-      <c r="B52" s="55"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
+      <c r="A52" s="56"/>
+      <c r="B52" s="56"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="55" t="s">
+      <c r="A53" s="56" t="s">
         <v>138</v>
       </c>
-      <c r="B53" s="55" t="s">
+      <c r="B53" s="56" t="s">
         <v>138</v>
       </c>
-      <c r="C53" s="30" t="s">
+      <c r="C53" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="D53" s="31"/>
-      <c r="E53" s="37" t="s">
+      <c r="D53" s="32"/>
+      <c r="E53" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F53" s="58" t="s">
+      <c r="F53" s="59" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="30"/>
+      <c r="G53" s="31"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="55" t="s">
+      <c r="A54" s="56" t="s">
         <v>141</v>
       </c>
-      <c r="B54" s="55" t="s">
+      <c r="B54" s="56" t="s">
         <v>141</v>
       </c>
-      <c r="C54" s="30" t="s">
+      <c r="C54" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="D54" s="31" t="s">
+      <c r="D54" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E54" s="31" t="s">
+      <c r="E54" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F54" s="30" t="s">
+      <c r="F54" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="G54" s="30"/>
+      <c r="G54" s="31"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="55" t="s">
+      <c r="A55" s="56" t="s">
         <v>144</v>
       </c>
-      <c r="B55" s="55" t="s">
+      <c r="B55" s="56" t="s">
         <v>145</v>
       </c>
-      <c r="C55" s="30" t="s">
+      <c r="C55" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="D55" s="31" t="s">
+      <c r="D55" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E55" s="31" t="s">
+      <c r="E55" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F55" s="30" t="s">
+      <c r="F55" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="G55" s="30"/>
+      <c r="G55" s="31"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="55" t="s">
+      <c r="A56" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="D56" s="31"/>
-      <c r="E56" s="31"/>
-      <c r="F56" s="30"/>
-      <c r="G56" s="30"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="31"/>
+      <c r="G56" s="31"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="55" t="s">
+      <c r="A57" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="B57" s="55" t="s">
+      <c r="B57" s="56" t="s">
         <v>149</v>
       </c>
-      <c r="C57" s="30" t="s">
+      <c r="C57" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="D57" s="31" t="s">
+      <c r="D57" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E57" s="31" t="s">
+      <c r="E57" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="F57" s="58" t="s">
+      <c r="F57" s="59" t="s">
         <v>151</v>
       </c>
-      <c r="G57" s="30"/>
+      <c r="G57" s="31"/>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="55" t="s">
+      <c r="A58" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="B58" s="55" t="s">
+      <c r="B58" s="56" t="s">
         <v>153</v>
       </c>
-      <c r="C58" s="30" t="s">
+      <c r="C58" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31" t="s">
+      <c r="D58" s="32"/>
+      <c r="E58" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="F58" s="36" t="s">
+      <c r="F58" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="G58" s="59" t="s">
+      <c r="G58" s="60" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="55" t="s">
+      <c r="A59" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="B59" s="55" t="s">
+      <c r="B59" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="C59" s="30" t="s">
+      <c r="C59" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31" t="s">
+      <c r="D59" s="32"/>
+      <c r="E59" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="F59" s="36" t="s">
+      <c r="F59" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="G59" s="60"/>
+      <c r="G59" s="61"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="55" t="s">
+      <c r="A60" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="B60" s="55" t="s">
+      <c r="B60" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="C60" s="30" t="s">
+      <c r="C60" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="D60" s="31"/>
-      <c r="E60" s="31" t="s">
+      <c r="D60" s="32"/>
+      <c r="E60" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="F60" s="36" t="s">
+      <c r="F60" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="G60" s="60"/>
+      <c r="G60" s="61"/>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="55" t="s">
+      <c r="A61" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="B61" s="55" t="s">
+      <c r="B61" s="56" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="30" t="s">
+      <c r="C61" s="31" t="s">
         <v>166</v>
       </c>
-      <c r="D61" s="31" t="s">
+      <c r="D61" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E61" s="31" t="s">
+      <c r="E61" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="F61" s="36" t="s">
+      <c r="F61" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="G61" s="60"/>
+      <c r="G61" s="61"/>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="55" t="s">
+      <c r="A62" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="B62" s="55" t="s">
+      <c r="B62" s="56" t="s">
         <v>168</v>
       </c>
-      <c r="C62" s="30" t="s">
+      <c r="C62" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="D62" s="31" t="s">
+      <c r="D62" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E62" s="31" t="s">
+      <c r="E62" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="F62" s="36" t="s">
+      <c r="F62" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="G62" s="61"/>
+      <c r="G62" s="62"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="55" t="s">
+      <c r="A63" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="55"/>
-      <c r="C63" s="30"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="31"/>
-      <c r="F63" s="30"/>
-      <c r="G63" s="30"/>
+      <c r="B63" s="56"/>
+      <c r="C63" s="31"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="31"/>
+      <c r="G63" s="31"/>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="55" t="s">
+      <c r="A64" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="B64" s="55"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="30"/>
+      <c r="B64" s="56"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31"/>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="55" t="s">
+      <c r="A65" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="B65" s="55" t="s">
+      <c r="B65" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="C65" s="30" t="s">
+      <c r="C65" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="D65" s="31" t="s">
+      <c r="D65" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E65" s="31" t="s">
+      <c r="E65" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F65" s="30" t="s">
+      <c r="F65" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="G65" s="30"/>
+      <c r="G65" s="31"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="55" t="s">
+      <c r="A66" s="56" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="55"/>
-      <c r="C66" s="30"/>
-      <c r="D66" s="31"/>
-      <c r="E66" s="31"/>
-      <c r="F66" s="30"/>
-      <c r="G66" s="30"/>
+      <c r="B66" s="56"/>
+      <c r="C66" s="31"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="32"/>
+      <c r="F66" s="31"/>
+      <c r="G66" s="31"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="55" t="s">
+      <c r="A67" s="56" t="s">
         <v>153</v>
       </c>
-      <c r="B67" s="55" t="s">
+      <c r="B67" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="C67" s="30" t="s">
+      <c r="C67" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="D67" s="31" t="s">
+      <c r="D67" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E67" s="31" t="s">
+      <c r="E67" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F67" s="30" t="s">
+      <c r="F67" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="G67" s="30"/>
+      <c r="G67" s="31"/>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="55" t="s">
+      <c r="A68" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="B68" s="55" t="s">
+      <c r="B68" s="56" t="s">
         <v>137</v>
       </c>
-      <c r="C68" s="30" t="s">
+      <c r="C68" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="D68" s="31" t="s">
+      <c r="D68" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E68" s="31" t="s">
+      <c r="E68" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F68" s="30" t="s">
+      <c r="F68" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="G68" s="30"/>
+      <c r="G68" s="31"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="55"/>
-      <c r="B69" s="55"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="31"/>
-      <c r="E69" s="31"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="30"/>
+      <c r="A69" s="56"/>
+      <c r="B69" s="56"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="32"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="55" t="s">
+      <c r="A70" s="56" t="s">
         <v>177</v>
       </c>
-      <c r="B70" s="55" t="s">
+      <c r="B70" s="56" t="s">
         <v>178</v>
       </c>
-      <c r="C70" s="30" t="s">
+      <c r="C70" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="D70" s="31" t="s">
+      <c r="D70" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E70" s="31" t="s">
+      <c r="E70" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F70" s="30" t="s">
+      <c r="F70" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="G70" s="30" t="s">
+      <c r="G70" s="31" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="55" t="s">
+      <c r="A71" s="56" t="s">
         <v>182</v>
       </c>
-      <c r="B71" s="55" t="s">
+      <c r="B71" s="56" t="s">
         <v>183</v>
       </c>
-      <c r="C71" s="30" t="s">
+      <c r="C71" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="D71" s="31" t="s">
+      <c r="D71" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E71" s="31" t="s">
+      <c r="E71" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F71" s="30" t="s">
+      <c r="F71" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="G71" s="30" t="s">
+      <c r="G71" s="31" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="55" t="s">
+      <c r="A72" s="56" t="s">
         <v>186</v>
       </c>
-      <c r="B72" s="55" t="s">
+      <c r="B72" s="56" t="s">
         <v>186</v>
       </c>
-      <c r="C72" s="30" t="s">
+      <c r="C72" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="D72" s="31" t="s">
+      <c r="D72" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="E72" s="31" t="s">
+      <c r="E72" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="30" t="s">
+      <c r="F72" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="G72" s="30"/>
+      <c r="G72" s="31"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="55" t="s">
+      <c r="A73" s="56" t="s">
         <v>189</v>
       </c>
-      <c r="B73" s="55" t="s">
+      <c r="B73" s="56" t="s">
         <v>189</v>
       </c>
-      <c r="C73" s="30" t="s">
+      <c r="C73" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="D73" s="31" t="s">
+      <c r="D73" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="E73" s="31" t="s">
+      <c r="E73" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="F73" s="30" t="s">
+      <c r="F73" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="G73" s="30"/>
+      <c r="G73" s="31"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="55" t="s">
+      <c r="A74" s="56" t="s">
         <v>191</v>
       </c>
-      <c r="B74" s="55" t="s">
+      <c r="B74" s="56" t="s">
         <v>191</v>
       </c>
-      <c r="C74" s="30" t="s">
+      <c r="C74" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="D74" s="31" t="s">
+      <c r="D74" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E74" s="37" t="s">
+      <c r="E74" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F74" s="30" t="s">
+      <c r="F74" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="G74" s="30"/>
+      <c r="G74" s="31"/>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="55" t="s">
+      <c r="A75" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="B75" s="55" t="s">
+      <c r="B75" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="C75" s="30" t="s">
+      <c r="C75" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31" t="s">
+      <c r="D75" s="32"/>
+      <c r="E75" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="F75" s="36" t="s">
+      <c r="F75" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="G75" s="58" t="s">
+      <c r="G75" s="59" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="55" t="s">
+      <c r="A76" s="56" t="s">
         <v>197</v>
       </c>
-      <c r="B76" s="55" t="s">
+      <c r="B76" s="56" t="s">
         <v>197</v>
       </c>
-      <c r="C76" s="30" t="s">
+      <c r="C76" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="D76" s="31" t="s">
+      <c r="D76" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E76" s="31" t="s">
+      <c r="E76" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="F76" s="30" t="s">
+      <c r="F76" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="G76" s="30"/>
+      <c r="G76" s="31"/>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="55" t="s">
+      <c r="A77" s="56" t="s">
         <v>200</v>
       </c>
-      <c r="B77" s="55" t="s">
+      <c r="B77" s="56" t="s">
         <v>200</v>
       </c>
-      <c r="C77" s="30" t="s">
+      <c r="C77" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="D77" s="31" t="s">
+      <c r="D77" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E77" s="31" t="s">
+      <c r="E77" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F77" s="30" t="s">
+      <c r="F77" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="G77" s="30"/>
+      <c r="G77" s="31"/>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="55" t="s">
+      <c r="A78" s="56" t="s">
         <v>203</v>
       </c>
-      <c r="B78" s="55" t="s">
+      <c r="B78" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="C78" s="30" t="s">
+      <c r="C78" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="D78" s="31" t="s">
+      <c r="D78" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E78" s="31" t="s">
+      <c r="E78" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="F78" s="30" t="s">
+      <c r="F78" s="31" t="s">
         <v>205</v>
       </c>
-      <c r="G78" s="30"/>
+      <c r="G78" s="31"/>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="55" t="s">
+      <c r="A79" s="56" t="s">
         <v>206</v>
       </c>
-      <c r="B79" s="55" t="s">
+      <c r="B79" s="56" t="s">
         <v>206</v>
       </c>
-      <c r="C79" s="30" t="s">
+      <c r="C79" s="31" t="s">
         <v>207</v>
       </c>
-      <c r="D79" s="31" t="s">
+      <c r="D79" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E79" s="31" t="s">
+      <c r="E79" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="F79" s="30" t="s">
+      <c r="F79" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="G79" s="30"/>
+      <c r="G79" s="31"/>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="55" t="s">
+      <c r="A80" s="56" t="s">
         <v>209</v>
       </c>
-      <c r="B80" s="55" t="s">
+      <c r="B80" s="56" t="s">
         <v>210</v>
       </c>
-      <c r="C80" s="30" t="s">
+      <c r="C80" s="31" t="s">
         <v>211</v>
       </c>
-      <c r="D80" s="31" t="s">
+      <c r="D80" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E80" s="31" t="s">
+      <c r="E80" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="F80" s="30" t="s">
+      <c r="F80" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="G80" s="30"/>
+      <c r="G80" s="31"/>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" s="55" t="s">
+      <c r="A81" s="56" t="s">
         <v>210</v>
       </c>
-      <c r="B81" s="55" t="s">
+      <c r="B81" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="C81" s="30" t="s">
+      <c r="C81" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="D81" s="31" t="s">
+      <c r="D81" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="E81" s="31" t="s">
+      <c r="E81" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="F81" s="30" t="s">
+      <c r="F81" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="G81" s="30"/>
+      <c r="G81" s="31"/>
     </row>
     <row r="82" spans="1:7">
-      <c r="A82" s="55" t="s">
+      <c r="A82" s="56" t="s">
         <v>217</v>
       </c>
-      <c r="B82" s="55" t="s">
+      <c r="B82" s="56" t="s">
         <v>218</v>
       </c>
-      <c r="C82" s="30" t="s">
+      <c r="C82" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="D82" s="31" t="s">
+      <c r="D82" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="E82" s="31" t="s">
+      <c r="E82" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="F82" s="30" t="s">
+      <c r="F82" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="G82" s="30"/>
+      <c r="G82" s="31"/>
     </row>
     <row r="83" spans="1:7">
-      <c r="A83" s="55" t="s">
+      <c r="A83" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="B83" s="55" t="s">
+      <c r="B83" s="56" t="s">
         <v>220</v>
       </c>
-      <c r="C83" s="36" t="s">
+      <c r="C83" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="D83" s="31" t="s">
+      <c r="D83" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="E83" s="31" t="s">
+      <c r="E83" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="F83" s="30" t="s">
+      <c r="F83" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="G83" s="30" t="s">
+      <c r="G83" s="31" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="55" t="s">
+      <c r="A84" s="56" t="s">
         <v>223</v>
       </c>
-      <c r="B84" s="55" t="s">
+      <c r="B84" s="56" t="s">
         <v>224</v>
       </c>
-      <c r="C84" s="36" t="s">
+      <c r="C84" s="37" t="s">
         <v>225</v>
       </c>
-      <c r="D84" s="31" t="s">
+      <c r="D84" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="E84" s="31" t="s">
+      <c r="E84" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="F84" s="30" t="s">
+      <c r="F84" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="G84" s="30" t="s">
+      <c r="G84" s="31" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="55" t="s">
+      <c r="A85" s="56" t="s">
         <v>227</v>
       </c>
-      <c r="B85" s="55" t="s">
+      <c r="B85" s="56" t="s">
         <v>227</v>
       </c>
-      <c r="C85" s="30" t="s">
+      <c r="C85" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="D85" s="31" t="s">
+      <c r="D85" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E85" s="37" t="s">
+      <c r="E85" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="F85" s="30" t="s">
+      <c r="F85" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="G85" s="30"/>
+      <c r="G85" s="31"/>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="55"/>
-      <c r="B86" s="55"/>
-      <c r="C86" s="30"/>
-      <c r="D86" s="31"/>
-      <c r="E86" s="31"/>
-      <c r="F86" s="30"/>
-      <c r="G86" s="30"/>
+      <c r="A86" s="56"/>
+      <c r="B86" s="56"/>
+      <c r="C86" s="31"/>
+      <c r="D86" s="32"/>
+      <c r="E86" s="32"/>
+      <c r="F86" s="31"/>
+      <c r="G86" s="31"/>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" s="55" t="s">
+      <c r="A87" s="56" t="s">
         <v>230</v>
       </c>
-      <c r="B87" s="55"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="31"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
+      <c r="B87" s="56"/>
+      <c r="C87" s="31"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="32"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31"/>
     </row>
     <row r="88" spans="1:7">
-      <c r="A88" s="55" t="s">
+      <c r="A88" s="56" t="s">
         <v>231</v>
       </c>
-      <c r="B88" s="55"/>
-      <c r="C88" s="30"/>
-      <c r="D88" s="31"/>
-      <c r="E88" s="31"/>
-      <c r="F88" s="30"/>
-      <c r="G88" s="30"/>
+      <c r="B88" s="56"/>
+      <c r="C88" s="31"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="32"/>
+      <c r="F88" s="31"/>
+      <c r="G88" s="31"/>
     </row>
     <row r="91" spans="1:7">
-      <c r="A91" s="55" t="s">
+      <c r="A91" s="56" t="s">
         <v>232</v>
       </c>
-      <c r="B91" s="55" t="s">
+      <c r="B91" s="56" t="s">
         <v>233</v>
       </c>
-      <c r="C91" s="30" t="s">
+      <c r="C91" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="D91" s="31" t="s">
+      <c r="D91" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E91" s="31" t="s">
+      <c r="E91" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F91" s="30" t="s">
+      <c r="F91" s="31" t="s">
         <v>235</v>
       </c>
       <c r="G91" t="s">
@@ -4835,22 +4839,22 @@
       </c>
     </row>
     <row r="92" spans="1:7">
-      <c r="A92" s="55" t="s">
+      <c r="A92" s="56" t="s">
         <v>232</v>
       </c>
-      <c r="B92" s="55" t="s">
+      <c r="B92" s="56" t="s">
         <v>237</v>
       </c>
-      <c r="C92" s="30" t="s">
+      <c r="C92" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="D92" s="31" t="s">
+      <c r="D92" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E92" s="31" t="s">
+      <c r="E92" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F92" s="30" t="s">
+      <c r="F92" s="31" t="s">
         <v>235</v>
       </c>
       <c r="G92" t="s">
@@ -4858,7 +4862,7 @@
       </c>
     </row>
     <row r="93" spans="1:7">
-      <c r="D93" s="27" t="s">
+      <c r="D93" s="28" t="s">
         <v>240</v>
       </c>
     </row>
@@ -4882,7 +4886,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="28.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="18.2685185185185" style="27" customWidth="1"/>
+    <col min="3" max="3" width="18.2685185185185" style="28" customWidth="1"/>
     <col min="4" max="4" width="17.0648148148148" customWidth="1"/>
     <col min="5" max="5" width="72" customWidth="1"/>
     <col min="6" max="6" width="23.462962962963" customWidth="1"/>
@@ -4890,1362 +4894,1362 @@
     <col min="8" max="8" width="31.6018518518519" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="25" customFormat="1" ht="28.5" customHeight="1" spans="1:7">
-      <c r="A1" s="28" t="s">
+    <row r="1" s="26" customFormat="1" ht="28.5" customHeight="1" spans="1:7">
+      <c r="A1" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="29" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>245</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="31" t="s">
         <v>248</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-    </row>
-    <row r="6" s="26" customFormat="1" spans="1:7">
-      <c r="A6" s="32" t="s">
+      <c r="C5" s="32"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+    </row>
+    <row r="6" s="27" customFormat="1" spans="1:7">
+      <c r="A6" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32" t="s">
+      <c r="D6" s="33"/>
+      <c r="E6" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-    </row>
-    <row r="7" s="26" customFormat="1" spans="1:7">
-      <c r="A7" s="32" t="s">
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+    </row>
+    <row r="7" s="27" customFormat="1" spans="1:7">
+      <c r="A7" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32" t="s">
+      <c r="D7" s="33"/>
+      <c r="E7" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-    </row>
-    <row r="8" s="26" customFormat="1" spans="1:7">
-      <c r="A8" s="32" t="s">
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+    </row>
+    <row r="8" s="27" customFormat="1" spans="1:7">
+      <c r="A8" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32" t="s">
+      <c r="D8" s="33"/>
+      <c r="E8" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-    </row>
-    <row r="9" s="26" customFormat="1" spans="1:7">
-      <c r="A9" s="32" t="s">
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+    </row>
+    <row r="9" s="27" customFormat="1" spans="1:7">
+      <c r="A9" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32" t="s">
+      <c r="D9" s="33"/>
+      <c r="E9" s="33" t="s">
         <v>250</v>
       </c>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36" t="s">
+      <c r="F10" s="37"/>
+      <c r="G10" s="37" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="37" t="s">
         <v>255</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36" t="s">
+      <c r="D13" s="37"/>
+      <c r="E13" s="37" t="s">
         <v>256</v>
       </c>
-      <c r="F13" s="36"/>
-      <c r="G13" s="38" t="s">
+      <c r="F13" s="37"/>
+      <c r="G13" s="39" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="37" t="s">
         <v>258</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36" t="s">
+      <c r="D14" s="37"/>
+      <c r="E14" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="F14" s="36"/>
-      <c r="G14" s="38" t="s">
+      <c r="F14" s="37"/>
+      <c r="G14" s="39" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="35" t="s">
+      <c r="A17" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35" t="s">
+      <c r="D17" s="36"/>
+      <c r="E17" s="36" t="s">
         <v>263</v>
       </c>
-      <c r="F17" s="36"/>
-      <c r="G17" s="38" t="s">
+      <c r="F17" s="37"/>
+      <c r="G17" s="39" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="30"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
+      <c r="A18" s="31"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32" t="s">
+      <c r="D19" s="33"/>
+      <c r="E19" s="33" t="s">
         <v>265</v>
       </c>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35" t="s">
+      <c r="D20" s="36"/>
+      <c r="E20" s="36" t="s">
         <v>266</v>
       </c>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36" t="s">
+      <c r="F20" s="37"/>
+      <c r="G20" s="37" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35" t="s">
+      <c r="D21" s="36"/>
+      <c r="E21" s="36" t="s">
         <v>268</v>
       </c>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36" t="s">
+      <c r="F21" s="37"/>
+      <c r="G21" s="37" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="36" t="s">
+      <c r="A22" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36" t="s">
+      <c r="C22" s="38"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37" t="s">
         <v>270</v>
       </c>
-      <c r="F22" s="41" t="s">
+      <c r="F22" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="G22" s="36"/>
+      <c r="G22" s="37"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36" t="s">
+      <c r="C23" s="38"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37" t="s">
         <v>270</v>
       </c>
-      <c r="F23" s="42"/>
-      <c r="G23" s="36"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="37"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="38" t="s">
+      <c r="A24" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="40" t="s">
         <v>271</v>
       </c>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35" t="s">
+      <c r="D24" s="36"/>
+      <c r="E24" s="36" t="s">
         <v>272</v>
       </c>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="35" t="s">
+      <c r="A25" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="35" t="s">
+      <c r="B25" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35" t="s">
+      <c r="D25" s="36"/>
+      <c r="E25" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="F25" s="36"/>
-      <c r="G25" s="38" t="s">
+      <c r="F25" s="37"/>
+      <c r="G25" s="39" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="31" t="s">
         <v>274</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="32" t="s">
         <v>271</v>
       </c>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30" t="s">
+      <c r="D26" s="31"/>
+      <c r="E26" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30" t="s">
+      <c r="F26" s="31"/>
+      <c r="G26" s="31" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="32" t="s">
+      <c r="B27" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32" t="s">
+      <c r="D27" s="33"/>
+      <c r="E27" s="33" t="s">
         <v>277</v>
       </c>
-      <c r="F27" s="36"/>
-      <c r="G27" s="38" t="s">
+      <c r="F27" s="37"/>
+      <c r="G27" s="39" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="40" t="s">
         <v>271</v>
       </c>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35" t="s">
+      <c r="D28" s="36"/>
+      <c r="E28" s="36" t="s">
         <v>278</v>
       </c>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36" t="s">
+      <c r="F28" s="37"/>
+      <c r="G28" s="37" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="35" t="s">
+      <c r="A29" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="B29" s="35" t="s">
+      <c r="B29" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35" t="s">
+      <c r="D29" s="36"/>
+      <c r="E29" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="37" t="s">
+      <c r="C30" s="38" t="s">
         <v>271</v>
       </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36" t="s">
+      <c r="D30" s="37"/>
+      <c r="E30" s="37" t="s">
         <v>280</v>
       </c>
-      <c r="F30" s="43"/>
-      <c r="G30" s="38" t="s">
+      <c r="F30" s="44"/>
+      <c r="G30" s="39" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="31" t="s">
         <v>281</v>
       </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="30"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="31"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="30" t="s">
+      <c r="A32" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="30" t="s">
+      <c r="B32" s="31" t="s">
         <v>282</v>
       </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="30"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="31"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="30" t="s">
+      <c r="B33" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="30"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="31"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="30" t="s">
+      <c r="B34" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="30"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="31"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="30"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="30"/>
+      <c r="A35" s="31"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="31"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="B36" s="30" t="s">
+      <c r="B36" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="C36" s="31"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="30"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="31"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="30" t="s">
+      <c r="A37" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="30" t="s">
+      <c r="B37" s="31" t="s">
         <v>286</v>
       </c>
-      <c r="C37" s="31"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="44"/>
-      <c r="G37" s="30"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="31"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="30" t="s">
+      <c r="A38" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="31" t="s">
         <v>287</v>
       </c>
-      <c r="C38" s="31"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="30"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="31"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="30" t="s">
+      <c r="B39" s="31" t="s">
         <v>288</v>
       </c>
-      <c r="C39" s="31"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="30"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="31"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="36" t="s">
+      <c r="A40" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="36" t="s">
+      <c r="B40" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="C40" s="37"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="38" t="s">
+      <c r="C40" s="38"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="39" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="30" t="s">
+      <c r="A41" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="B41" s="30" t="s">
+      <c r="B41" s="31" t="s">
         <v>290</v>
       </c>
-      <c r="C41" s="31"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="30"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="31"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="B42" s="30" t="s">
+      <c r="B42" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="C42" s="31"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="30"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="31"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="30" t="s">
+      <c r="A43" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="B43" s="30" t="s">
+      <c r="B43" s="31" t="s">
         <v>292</v>
       </c>
-      <c r="C43" s="31"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="30"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="31"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="35" t="s">
+      <c r="A44" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="35" t="s">
+      <c r="B44" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="39" t="s">
+      <c r="C44" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="D44" s="35"/>
-      <c r="E44" s="35" t="s">
+      <c r="D44" s="36"/>
+      <c r="E44" s="36" t="s">
         <v>293</v>
       </c>
-      <c r="F44" s="45"/>
-      <c r="G44" s="36" t="s">
+      <c r="F44" s="46"/>
+      <c r="G44" s="37" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="35" t="s">
+      <c r="A45" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="B45" s="35" t="s">
+      <c r="B45" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="C45" s="39" t="s">
+      <c r="C45" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="D45" s="35"/>
-      <c r="E45" s="35" t="s">
+      <c r="D45" s="36"/>
+      <c r="E45" s="36" t="s">
         <v>293</v>
       </c>
-      <c r="F45" s="36"/>
-      <c r="G45" s="36"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="35" t="s">
+      <c r="A46" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="B46" s="35" t="s">
+      <c r="B46" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="C46" s="39" t="s">
+      <c r="C46" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35" t="s">
+      <c r="D46" s="36"/>
+      <c r="E46" s="36" t="s">
         <v>295</v>
       </c>
-      <c r="F46" s="46" t="s">
+      <c r="F46" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="G46" s="36" t="s">
+      <c r="G46" s="37" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="47" ht="14.65" customHeight="1" spans="1:7">
-      <c r="A47" s="35" t="s">
+      <c r="A47" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="35" t="s">
+      <c r="B47" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="C47" s="39" t="s">
+      <c r="C47" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="D47" s="35"/>
-      <c r="E47" s="35" t="s">
+      <c r="D47" s="36"/>
+      <c r="E47" s="36" t="s">
         <v>295</v>
       </c>
-      <c r="F47" s="47"/>
-      <c r="G47" s="36"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="37"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="36" t="s">
+      <c r="A48" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="B48" s="36" t="s">
+      <c r="B48" s="37" t="s">
         <v>297</v>
       </c>
-      <c r="C48" s="37" t="s">
+      <c r="C48" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36" t="s">
+      <c r="D48" s="37"/>
+      <c r="E48" s="37" t="s">
         <v>298</v>
       </c>
-      <c r="F48" s="36"/>
-      <c r="G48" s="38" t="s">
+      <c r="F48" s="37"/>
+      <c r="G48" s="39" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="36" t="s">
+      <c r="A49" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="B49" s="36" t="s">
+      <c r="B49" s="37" t="s">
         <v>300</v>
       </c>
-      <c r="C49" s="37" t="s">
+      <c r="C49" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="D49" s="36"/>
-      <c r="E49" s="36" t="s">
+      <c r="D49" s="37"/>
+      <c r="E49" s="37" t="s">
         <v>298</v>
       </c>
-      <c r="F49" s="36"/>
-      <c r="G49" s="38"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="39"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="36" t="s">
+      <c r="A50" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="B50" s="36" t="s">
+      <c r="B50" s="37" t="s">
         <v>301</v>
       </c>
-      <c r="C50" s="37" t="s">
+      <c r="C50" s="38" t="s">
         <v>271</v>
       </c>
-      <c r="D50" s="36"/>
-      <c r="E50" s="36" t="s">
+      <c r="D50" s="37"/>
+      <c r="E50" s="37" t="s">
         <v>302</v>
       </c>
-      <c r="F50" s="36"/>
-      <c r="G50" s="38"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="39"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="36" t="s">
+      <c r="A51" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="B51" s="36" t="s">
+      <c r="B51" s="37" t="s">
         <v>303</v>
       </c>
-      <c r="C51" s="37" t="s">
+      <c r="C51" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="D51" s="36"/>
-      <c r="E51" s="36" t="s">
+      <c r="D51" s="37"/>
+      <c r="E51" s="37" t="s">
         <v>304</v>
       </c>
-      <c r="F51" s="36"/>
-      <c r="G51" s="38"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="39"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="30"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
+      <c r="A52" s="31"/>
+      <c r="B52" s="31"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="30" t="s">
+      <c r="A53" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="B53" s="30" t="s">
+      <c r="B53" s="31" t="s">
         <v>305</v>
       </c>
-      <c r="C53" s="31"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="30"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="30" t="s">
+      <c r="A54" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="B54" s="30" t="s">
+      <c r="B54" s="31" t="s">
         <v>306</v>
       </c>
-      <c r="C54" s="31"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="31"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="31"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="30" t="s">
+      <c r="A55" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="B55" s="30" t="s">
+      <c r="B55" s="31" t="s">
         <v>307</v>
       </c>
-      <c r="C55" s="31"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="30" t="s">
+      <c r="A56" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="B56" s="30" t="s">
+      <c r="B56" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="C56" s="31"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="30"/>
-      <c r="G56" s="30"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="31"/>
+      <c r="E56" s="31"/>
+      <c r="F56" s="31"/>
+      <c r="G56" s="31"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="35" t="s">
+      <c r="A57" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="B57" s="35" t="s">
+      <c r="B57" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="C57" s="39" t="s">
+      <c r="C57" s="40" t="s">
         <v>271</v>
       </c>
-      <c r="D57" s="35"/>
-      <c r="E57" s="35" t="s">
+      <c r="D57" s="36"/>
+      <c r="E57" s="36" t="s">
         <v>309</v>
       </c>
-      <c r="F57" s="36"/>
-      <c r="G57" s="36" t="s">
+      <c r="F57" s="37"/>
+      <c r="G57" s="37" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="B58" s="30" t="s">
+      <c r="B58" s="31" t="s">
         <v>311</v>
       </c>
-      <c r="C58" s="31"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="30" t="s">
+      <c r="A59" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="B59" s="30" t="s">
+      <c r="B59" s="31" t="s">
         <v>312</v>
       </c>
-      <c r="C59" s="31"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="30"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="31"/>
+      <c r="F59" s="31"/>
+      <c r="G59" s="31"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="30" t="s">
+      <c r="A60" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="B60" s="30" t="s">
+      <c r="B60" s="31" t="s">
         <v>313</v>
       </c>
-      <c r="C60" s="31"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
-      <c r="F60" s="30"/>
-      <c r="G60" s="30"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="31"/>
+      <c r="E60" s="31"/>
+      <c r="F60" s="31"/>
+      <c r="G60" s="31"/>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="38" t="s">
+      <c r="A61" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="B61" s="38" t="s">
+      <c r="B61" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="48" t="s">
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="49" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="38" t="s">
+      <c r="A62" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="B62" s="38" t="s">
+      <c r="B62" s="39" t="s">
         <v>316</v>
       </c>
-      <c r="C62" s="31"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="30"/>
-      <c r="F62" s="30"/>
-      <c r="G62" s="49"/>
+      <c r="C62" s="32"/>
+      <c r="D62" s="31"/>
+      <c r="E62" s="31"/>
+      <c r="F62" s="31"/>
+      <c r="G62" s="50"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="30" t="s">
+      <c r="A63" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="30" t="s">
+      <c r="B63" s="31" t="s">
         <v>317</v>
       </c>
-      <c r="C63" s="31"/>
-      <c r="D63" s="30"/>
-      <c r="E63" s="30"/>
-      <c r="F63" s="30"/>
-      <c r="G63" s="30"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="31"/>
+      <c r="E63" s="31"/>
+      <c r="F63" s="31"/>
+      <c r="G63" s="31"/>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="30" t="s">
+      <c r="A64" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="B64" s="30" t="s">
+      <c r="B64" s="31" t="s">
         <v>318</v>
       </c>
-      <c r="C64" s="31"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="30"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31"/>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="36" t="s">
+      <c r="A65" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="B65" s="36" t="s">
+      <c r="B65" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="C65" s="37" t="s">
+      <c r="C65" s="38" t="s">
         <v>271</v>
       </c>
-      <c r="D65" s="36"/>
-      <c r="E65" s="36" t="s">
+      <c r="D65" s="37"/>
+      <c r="E65" s="37" t="s">
         <v>319</v>
       </c>
-      <c r="F65" s="36"/>
-      <c r="G65" s="38" t="s">
+      <c r="F65" s="37"/>
+      <c r="G65" s="39" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="30" t="s">
+      <c r="B66" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="C66" s="31"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="30"/>
-      <c r="F66" s="30"/>
-      <c r="G66" s="30"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="31"/>
+      <c r="E66" s="31"/>
+      <c r="F66" s="31"/>
+      <c r="G66" s="31"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="35" t="s">
+      <c r="A67" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="B67" s="35" t="s">
+      <c r="B67" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="C67" s="39" t="s">
+      <c r="C67" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="D67" s="35"/>
-      <c r="E67" s="35" t="s">
+      <c r="D67" s="36"/>
+      <c r="E67" s="36" t="s">
         <v>321</v>
       </c>
-      <c r="F67" s="36" t="s">
+      <c r="F67" s="37" t="s">
         <v>322</v>
       </c>
-      <c r="G67" s="36" t="s">
+      <c r="G67" s="37" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="35" t="s">
+      <c r="A68" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="B68" s="35" t="s">
+      <c r="B68" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="C68" s="39" t="s">
+      <c r="C68" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="D68" s="35"/>
-      <c r="E68" s="35" t="s">
+      <c r="D68" s="36"/>
+      <c r="E68" s="36" t="s">
         <v>321</v>
       </c>
-      <c r="F68" s="36" t="s">
+      <c r="F68" s="37" t="s">
         <v>322</v>
       </c>
-      <c r="G68" s="36" t="s">
+      <c r="G68" s="37" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="30"/>
-      <c r="B69" s="30"/>
-      <c r="C69" s="31"/>
-      <c r="D69" s="30"/>
-      <c r="E69" s="30"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="30"/>
+      <c r="A69" s="31"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="32"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="35" t="s">
+      <c r="A70" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="B70" s="35" t="s">
+      <c r="B70" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="C70" s="39"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="35" t="s">
+      <c r="C70" s="40"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="36" t="s">
         <v>325</v>
       </c>
-      <c r="F70" s="36"/>
-      <c r="G70" s="38" t="s">
+      <c r="F70" s="37"/>
+      <c r="G70" s="39" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="35" t="s">
+      <c r="A71" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="B71" s="35" t="s">
+      <c r="B71" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="C71" s="39"/>
-      <c r="D71" s="35"/>
-      <c r="E71" s="35" t="s">
+      <c r="C71" s="40"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="36" t="s">
         <v>326</v>
       </c>
-      <c r="F71" s="36"/>
-      <c r="G71" s="38" t="s">
+      <c r="F71" s="37"/>
+      <c r="G71" s="39" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="35" t="s">
+      <c r="A72" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="B72" s="35" t="s">
+      <c r="B72" s="36" t="s">
         <v>187</v>
       </c>
-      <c r="C72" s="39" t="s">
+      <c r="C72" s="40" t="s">
         <v>242</v>
       </c>
-      <c r="D72" s="35"/>
-      <c r="E72" s="35" t="s">
+      <c r="D72" s="36"/>
+      <c r="E72" s="36" t="s">
         <v>327</v>
       </c>
-      <c r="F72" s="36"/>
-      <c r="G72" s="36"/>
+      <c r="F72" s="37"/>
+      <c r="G72" s="37"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="35" t="s">
+      <c r="A73" s="36" t="s">
         <v>189</v>
       </c>
-      <c r="B73" s="35" t="s">
+      <c r="B73" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="C73" s="39" t="s">
+      <c r="C73" s="40" t="s">
         <v>271</v>
       </c>
-      <c r="D73" s="35"/>
-      <c r="E73" s="35" t="s">
+      <c r="D73" s="36"/>
+      <c r="E73" s="36" t="s">
         <v>327</v>
       </c>
-      <c r="F73" s="36"/>
-      <c r="G73" s="36"/>
+      <c r="F73" s="37"/>
+      <c r="G73" s="37"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="36" t="s">
+      <c r="A74" s="37" t="s">
         <v>191</v>
       </c>
-      <c r="B74" s="36" t="s">
+      <c r="B74" s="37" t="s">
         <v>328</v>
       </c>
-      <c r="C74" s="37" t="s">
+      <c r="C74" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="D74" s="36"/>
-      <c r="E74" s="36" t="s">
+      <c r="D74" s="37"/>
+      <c r="E74" s="37" t="s">
         <v>329</v>
       </c>
-      <c r="F74" s="36"/>
-      <c r="G74" s="38" t="s">
+      <c r="F74" s="37"/>
+      <c r="G74" s="39" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="36" t="s">
+      <c r="A75" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="B75" s="36" t="s">
+      <c r="B75" s="37" t="s">
         <v>331</v>
       </c>
-      <c r="C75" s="37" t="s">
+      <c r="C75" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="D75" s="36"/>
-      <c r="E75" s="36" t="s">
+      <c r="D75" s="37"/>
+      <c r="E75" s="37" t="s">
         <v>332</v>
       </c>
-      <c r="F75" s="36"/>
-      <c r="G75" s="36"/>
+      <c r="F75" s="37"/>
+      <c r="G75" s="37"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="36" t="s">
+      <c r="A76" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="B76" s="36" t="s">
+      <c r="B76" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="C76" s="37" t="s">
+      <c r="C76" s="38" t="s">
         <v>271</v>
       </c>
-      <c r="D76" s="36"/>
-      <c r="E76" s="36" t="s">
+      <c r="D76" s="37"/>
+      <c r="E76" s="37" t="s">
         <v>333</v>
       </c>
-      <c r="F76" s="36"/>
-      <c r="G76" s="38" t="s">
+      <c r="F76" s="37"/>
+      <c r="G76" s="39" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="36" t="s">
+      <c r="A77" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="B77" s="36" t="s">
+      <c r="B77" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="C77" s="37"/>
-      <c r="D77" s="36"/>
-      <c r="E77" s="36"/>
-      <c r="F77" s="36"/>
-      <c r="G77" s="38" t="s">
+      <c r="C77" s="38"/>
+      <c r="D77" s="37"/>
+      <c r="E77" s="37"/>
+      <c r="F77" s="37"/>
+      <c r="G77" s="39" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="36" t="s">
+      <c r="A78" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="B78" s="36" t="s">
+      <c r="B78" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="C78" s="37"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-      <c r="G78" s="38" t="s">
+      <c r="C78" s="38"/>
+      <c r="D78" s="37"/>
+      <c r="E78" s="37"/>
+      <c r="F78" s="37"/>
+      <c r="G78" s="39" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="36" t="s">
+      <c r="A79" s="37" t="s">
         <v>206</v>
       </c>
-      <c r="B79" s="36" t="s">
+      <c r="B79" s="37" t="s">
         <v>335</v>
       </c>
-      <c r="C79" s="37" t="s">
+      <c r="C79" s="38" t="s">
         <v>249</v>
       </c>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36" t="s">
+      <c r="D79" s="37"/>
+      <c r="E79" s="37" t="s">
         <v>336</v>
       </c>
-      <c r="F79" s="36"/>
-      <c r="G79" s="38" t="s">
+      <c r="F79" s="37"/>
+      <c r="G79" s="39" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="30" t="s">
+      <c r="A80" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="B80" s="30" t="s">
+      <c r="B80" s="31" t="s">
         <v>211</v>
       </c>
-      <c r="C80" s="31"/>
-      <c r="D80" s="30"/>
-      <c r="E80" s="30"/>
-      <c r="F80" s="30"/>
-      <c r="G80" s="30" t="s">
+      <c r="C80" s="32"/>
+      <c r="D80" s="31"/>
+      <c r="E80" s="31"/>
+      <c r="F80" s="31"/>
+      <c r="G80" s="31" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" s="35" t="s">
+      <c r="A81" s="36" t="s">
         <v>210</v>
       </c>
-      <c r="B81" s="35" t="s">
+      <c r="B81" s="36" t="s">
         <v>207</v>
       </c>
-      <c r="C81" s="39" t="s">
+      <c r="C81" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="D81" s="35"/>
-      <c r="E81" s="35" t="s">
+      <c r="D81" s="36"/>
+      <c r="E81" s="36" t="s">
         <v>338</v>
       </c>
-      <c r="F81" s="35"/>
-      <c r="G81" s="38" t="s">
+      <c r="F81" s="36"/>
+      <c r="G81" s="39" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="82" spans="1:7">
-      <c r="A82" s="30" t="s">
+      <c r="A82" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="B82" s="30" t="s">
+      <c r="B82" s="31" t="s">
         <v>339</v>
       </c>
-      <c r="C82" s="31"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="30"/>
-      <c r="F82" s="30"/>
-      <c r="G82" s="30"/>
+      <c r="C82" s="32"/>
+      <c r="D82" s="31"/>
+      <c r="E82" s="31"/>
+      <c r="F82" s="31"/>
+      <c r="G82" s="31"/>
     </row>
     <row r="83" spans="1:7">
-      <c r="A83" s="30" t="s">
+      <c r="A83" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="B83" s="30" t="s">
+      <c r="B83" s="31" t="s">
         <v>340</v>
       </c>
-      <c r="C83" s="31"/>
-      <c r="D83" s="30"/>
-      <c r="E83" s="30"/>
-      <c r="F83" s="30"/>
-      <c r="G83" s="30"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="31"/>
+      <c r="E83" s="31"/>
+      <c r="F83" s="31"/>
+      <c r="G83" s="31"/>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="30" t="s">
+      <c r="A84" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="B84" s="30" t="s">
+      <c r="B84" s="31" t="s">
         <v>341</v>
       </c>
-      <c r="C84" s="31"/>
-      <c r="D84" s="30"/>
-      <c r="E84" s="30"/>
-      <c r="F84" s="30"/>
-      <c r="G84" s="30"/>
+      <c r="C84" s="32"/>
+      <c r="D84" s="31"/>
+      <c r="E84" s="31"/>
+      <c r="F84" s="31"/>
+      <c r="G84" s="31"/>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="30" t="s">
+      <c r="A85" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="B85" s="30" t="s">
+      <c r="B85" s="31" t="s">
         <v>342</v>
       </c>
-      <c r="C85" s="31"/>
-      <c r="D85" s="30"/>
-      <c r="E85" s="30"/>
-      <c r="F85" s="30"/>
-      <c r="G85" s="30"/>
+      <c r="C85" s="32"/>
+      <c r="D85" s="31"/>
+      <c r="E85" s="31"/>
+      <c r="F85" s="31"/>
+      <c r="G85" s="31"/>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="30"/>
-      <c r="B86" s="30"/>
-      <c r="C86" s="31"/>
-      <c r="D86" s="30"/>
-      <c r="E86" s="30"/>
-      <c r="F86" s="30"/>
-      <c r="G86" s="30"/>
+      <c r="A86" s="31"/>
+      <c r="B86" s="31"/>
+      <c r="C86" s="32"/>
+      <c r="D86" s="31"/>
+      <c r="E86" s="31"/>
+      <c r="F86" s="31"/>
+      <c r="G86" s="31"/>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" s="30" t="s">
+      <c r="A87" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="B87" s="30" t="s">
+      <c r="B87" s="31" t="s">
         <v>343</v>
       </c>
-      <c r="C87" s="31"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
+      <c r="C87" s="32"/>
+      <c r="D87" s="31"/>
+      <c r="E87" s="31"/>
+      <c r="F87" s="31"/>
+      <c r="G87" s="31"/>
     </row>
     <row r="88" spans="1:7">
-      <c r="A88" s="30" t="s">
+      <c r="A88" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="B88" s="30" t="s">
+      <c r="B88" s="31" t="s">
         <v>344</v>
       </c>
-      <c r="C88" s="31"/>
-      <c r="D88" s="30"/>
-      <c r="E88" s="30"/>
-      <c r="F88" s="30"/>
-      <c r="G88" s="30"/>
+      <c r="C88" s="32"/>
+      <c r="D88" s="31"/>
+      <c r="E88" s="31"/>
+      <c r="F88" s="31"/>
+      <c r="G88" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6685,7 +6689,7 @@
       <c r="F17" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="18" t="s">
         <v>400</v>
       </c>
       <c r="H17" s="4" t="s">
@@ -6829,7 +6833,7 @@
       <c r="F24" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="19" t="s">
         <v>415</v>
       </c>
       <c r="H24" s="4"/>
@@ -6853,7 +6857,7 @@
       <c r="F25" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="19" t="s">
         <v>418</v>
       </c>
       <c r="H25" s="4"/>
@@ -6925,7 +6929,7 @@
       <c r="F28" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G28" s="19" t="s">
+      <c r="G28" s="20" t="s">
         <v>427</v>
       </c>
       <c r="H28" s="11"/>
@@ -6947,7 +6951,7 @@
         <v>354</v>
       </c>
       <c r="F29" s="3"/>
-      <c r="G29" s="19"/>
+      <c r="G29" s="20"/>
       <c r="H29" s="11"/>
     </row>
     <row r="30" spans="1:8">
@@ -6969,7 +6973,7 @@
       <c r="F30" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G30" s="19" t="s">
+      <c r="G30" s="20" t="s">
         <v>432</v>
       </c>
       <c r="H30" s="15" t="s">
@@ -6993,7 +6997,7 @@
         <v>354</v>
       </c>
       <c r="F31" s="3"/>
-      <c r="G31" s="19"/>
+      <c r="G31" s="20"/>
       <c r="H31" s="17"/>
     </row>
     <row r="32" spans="1:8">
@@ -7022,7 +7026,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" ht="28.8" spans="1:8">
       <c r="A33" s="11">
         <v>34</v>
       </c>
@@ -7041,7 +7045,7 @@
       <c r="F33" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G33" s="16" t="s">
+      <c r="G33" s="10" t="s">
         <v>440</v>
       </c>
       <c r="H33" s="11"/>
@@ -7327,13 +7331,13 @@
       <c r="D46" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E46" s="21" t="s">
         <v>364</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G46" s="21" t="s">
+      <c r="G46" s="22" t="s">
         <v>371</v>
       </c>
       <c r="H46" s="4"/>
@@ -7383,7 +7387,7 @@
       <c r="F48" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="G48" s="22" t="s">
+      <c r="G48" s="23" t="s">
         <v>478</v>
       </c>
       <c r="H48" s="11"/>
@@ -7405,7 +7409,7 @@
         <v>364</v>
       </c>
       <c r="F49" s="17"/>
-      <c r="G49" s="23"/>
+      <c r="G49" s="24"/>
       <c r="H49" s="11"/>
     </row>
     <row r="50" spans="1:8">
@@ -7427,7 +7431,7 @@
       <c r="F50" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="G50" s="22" t="s">
+      <c r="G50" s="23" t="s">
         <v>483</v>
       </c>
       <c r="H50" s="11"/>
@@ -7449,7 +7453,7 @@
         <v>364</v>
       </c>
       <c r="F51" s="17"/>
-      <c r="G51" s="23"/>
+      <c r="G51" s="24"/>
       <c r="H51" s="11"/>
     </row>
     <row r="52" spans="1:8">
@@ -7469,10 +7473,10 @@
       <c r="B53" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="C53" s="24" t="s">
+      <c r="C53" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D53" s="24" t="s">
+      <c r="D53" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E53" s="11"/>
@@ -7487,10 +7491,10 @@
       <c r="B54" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="C54" s="24" t="s">
+      <c r="C54" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D54" s="24" t="s">
+      <c r="D54" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E54" s="11"/>
@@ -7505,10 +7509,10 @@
       <c r="B55" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="C55" s="24" t="s">
+      <c r="C55" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D55" s="24" t="s">
+      <c r="D55" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E55" s="11"/>
@@ -7523,10 +7527,10 @@
       <c r="B56" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="C56" s="24" t="s">
+      <c r="C56" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D56" s="24" t="s">
+      <c r="D56" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E56" s="11"/>
@@ -7541,10 +7545,10 @@
       <c r="B57" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="C57" s="24" t="s">
+      <c r="C57" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D57" s="24" t="s">
+      <c r="D57" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E57" s="11"/>
@@ -7559,10 +7563,10 @@
       <c r="B58" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="C58" s="24" t="s">
+      <c r="C58" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D58" s="24" t="s">
+      <c r="D58" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E58" s="11"/>
@@ -7577,10 +7581,10 @@
       <c r="B59" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="C59" s="24" t="s">
+      <c r="C59" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D59" s="24" t="s">
+      <c r="D59" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E59" s="11"/>
@@ -7595,10 +7599,10 @@
       <c r="B60" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="C60" s="24" t="s">
+      <c r="C60" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D60" s="24" t="s">
+      <c r="D60" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E60" s="11"/>
@@ -7613,10 +7617,10 @@
       <c r="B61" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="C61" s="24" t="s">
+      <c r="C61" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D61" s="24" t="s">
+      <c r="D61" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E61" s="11"/>
@@ -7631,10 +7635,10 @@
       <c r="B62" s="11" t="s">
         <v>494</v>
       </c>
-      <c r="C62" s="24" t="s">
+      <c r="C62" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D62" s="24" t="s">
+      <c r="D62" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E62" s="11"/>
@@ -7649,10 +7653,10 @@
       <c r="B63" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="C63" s="24" t="s">
+      <c r="C63" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D63" s="24" t="s">
+      <c r="D63" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E63" s="11"/>
@@ -7667,10 +7671,10 @@
       <c r="B64" s="11" t="s">
         <v>496</v>
       </c>
-      <c r="C64" s="24" t="s">
+      <c r="C64" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D64" s="24" t="s">
+      <c r="D64" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E64" s="11"/>
@@ -7685,10 +7689,10 @@
       <c r="B65" s="11" t="s">
         <v>497</v>
       </c>
-      <c r="C65" s="24" t="s">
+      <c r="C65" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D65" s="24" t="s">
+      <c r="D65" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E65" s="11"/>
@@ -7703,10 +7707,10 @@
       <c r="B66" s="11" t="s">
         <v>498</v>
       </c>
-      <c r="C66" s="24" t="s">
+      <c r="C66" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D66" s="24" t="s">
+      <c r="D66" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E66" s="11"/>
@@ -7721,10 +7725,10 @@
       <c r="B67" s="11" t="s">
         <v>499</v>
       </c>
-      <c r="C67" s="24" t="s">
+      <c r="C67" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D67" s="24" t="s">
+      <c r="D67" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E67" s="11"/>
@@ -7739,7 +7743,7 @@
       <c r="B68" s="11" t="s">
         <v>500</v>
       </c>
-      <c r="C68" s="24" t="s">
+      <c r="C68" s="25" t="s">
         <v>409</v>
       </c>
       <c r="D68" s="11" t="s">
@@ -7763,10 +7767,10 @@
       <c r="B69" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="C69" s="24" t="s">
+      <c r="C69" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D69" s="24" t="s">
+      <c r="D69" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E69" s="11"/>
@@ -7781,10 +7785,10 @@
       <c r="B70" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="C70" s="24" t="s">
+      <c r="C70" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D70" s="24" t="s">
+      <c r="D70" s="25" t="s">
         <v>409</v>
       </c>
       <c r="E70" s="11"/>

--- a/BPCOME-3502单片机需求260724a.xlsx
+++ b/BPCOME-3502单片机需求260724a.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LYT\潘工\BPCOME-3502-git\BPCOME-3502\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LYT\潘工\BPCOME-3502-git开机自启动\BPCOME-3502\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9767" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="5000-GPIO (2)" sheetId="1" state="hidden" r:id="rId1"/>
@@ -1351,7 +1351,8 @@
     <t>PWRBTN_OUT#</t>
   </si>
   <si>
-    <t>做输出给核心卡，当接收到PB4有20ms低电平或以上，就输出200ms低电平脉冲</t>
+    <t xml:space="preserve">做输出给核心卡，当接收到PB4有20ms低电平或以上，就输出200ms低电平脉冲 修改增加开机自启动，单片机初始化完成后输出一次200ms低脉冲，不用管PC0传来的信号
+</t>
   </si>
   <si>
     <t xml:space="preserve">PB6 </t>
@@ -2342,7 +2343,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2400,6 +2401,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3209,1629 +3213,1629 @@
   <dimension ref="A1:G93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="12.3333333333333" style="52" customWidth="1"/>
-    <col min="2" max="2" width="13" style="52" customWidth="1"/>
+    <col min="1" max="1" width="12.3333333333333" style="53" customWidth="1"/>
+    <col min="2" max="2" width="13" style="53" customWidth="1"/>
     <col min="3" max="3" width="23.7314814814815" customWidth="1"/>
-    <col min="4" max="4" width="9.73148148148148" style="28" customWidth="1"/>
-    <col min="5" max="5" width="10.7314814814815" style="28" customWidth="1"/>
+    <col min="4" max="4" width="9.73148148148148" style="29" customWidth="1"/>
+    <col min="5" max="5" width="10.7314814814815" style="29" customWidth="1"/>
     <col min="6" max="6" width="70" customWidth="1"/>
     <col min="7" max="7" width="95.6018518518518" customWidth="1"/>
     <col min="8" max="8" width="31.6018518518519" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="51" customFormat="1" ht="22.2" spans="1:7">
-      <c r="A1" s="53" t="s">
+    <row r="1" s="52" customFormat="1" ht="22.2" spans="1:7">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55" t="s">
+      <c r="E1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="55" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="38" t="s">
+      <c r="D2" s="33"/>
+      <c r="E2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="38" t="s">
+      <c r="D3" s="33"/>
+      <c r="E3" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="38" t="s">
+      <c r="D4" s="33"/>
+      <c r="E4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="32"/>
-      <c r="E5" s="38" t="s">
+      <c r="D5" s="33"/>
+      <c r="E5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="31"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="56" t="s">
+      <c r="A7" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="31"/>
+      <c r="G7" s="32"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="56" t="s">
+      <c r="B8" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="31"/>
+      <c r="G8" s="32"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="56" t="s">
+      <c r="A9" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="E9" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="31"/>
+      <c r="G9" s="32"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="31"/>
+      <c r="G10" s="32"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="31" t="s">
+      <c r="F11" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="31"/>
+      <c r="G11" s="32"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="56" t="s">
+      <c r="A12" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="31" t="s">
+      <c r="F12" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="31"/>
+      <c r="G12" s="32"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="56"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="56" t="s">
+      <c r="A15" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="56" t="s">
+      <c r="B15" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="56" t="s">
+      <c r="B16" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="31" t="s">
+      <c r="F17" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="31"/>
+      <c r="G17" s="32"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="56"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
+      <c r="A18" s="57"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="56" t="s">
+      <c r="A19" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="56" t="s">
+      <c r="B19" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="31" t="s">
+      <c r="F19" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="G19" s="31"/>
+      <c r="G19" s="32"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="C20" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="38" t="s">
+      <c r="D20" s="33"/>
+      <c r="E20" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="56" t="s">
+      <c r="A21" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="56" t="s">
+      <c r="B21" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="32" t="s">
+      <c r="E21" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="31" t="s">
+      <c r="F21" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="31"/>
+      <c r="G21" s="32"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="56" t="s">
+      <c r="A22" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="56" t="s">
+      <c r="B22" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="32" t="s">
+      <c r="E22" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="31" t="s">
+      <c r="F22" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="G22" s="31"/>
+      <c r="G22" s="32"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="56" t="s">
+      <c r="A23" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="56" t="s">
+      <c r="B23" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="C23" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="D23" s="32" t="s">
+      <c r="D23" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="32" t="s">
+      <c r="E23" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="31" t="s">
+      <c r="F23" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="G23" s="31"/>
+      <c r="G23" s="32"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="56" t="s">
+      <c r="A24" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="56" t="s">
+      <c r="B24" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="32" t="s">
+      <c r="E24" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="31" t="s">
+      <c r="F24" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="G24" s="31"/>
+      <c r="G24" s="32"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="56" t="s">
+      <c r="A25" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="56" t="s">
+      <c r="B25" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="32" t="s">
+      <c r="E25" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="F25" s="31" t="s">
+      <c r="F25" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="G25" s="31"/>
+      <c r="G25" s="32"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="57" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E26" s="32" t="s">
+      <c r="E26" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="31" t="s">
+      <c r="F26" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="G26" s="31"/>
+      <c r="G26" s="32"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="56" t="s">
+      <c r="A27" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="56" t="s">
+      <c r="B27" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="31" t="s">
+      <c r="C27" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E27" s="32" t="s">
+      <c r="E27" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="F27" s="31" t="s">
+      <c r="F27" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="G27" s="31"/>
+      <c r="G27" s="32"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="56" t="s">
+      <c r="B28" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="C28" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E28" s="32" t="s">
+      <c r="E28" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="F28" s="31" t="s">
+      <c r="F28" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="G28" s="31"/>
+      <c r="G28" s="32"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="56" t="s">
+      <c r="A29" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="B29" s="56" t="s">
+      <c r="B29" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="31" t="s">
+      <c r="C29" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="32" t="s">
+      <c r="E29" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="31" t="s">
+      <c r="F29" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="G29" s="31"/>
+      <c r="G29" s="32"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="56" t="s">
+      <c r="A30" s="57" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="56" t="s">
+      <c r="B30" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="32" t="s">
+      <c r="E30" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F30" s="31" t="s">
+      <c r="F30" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="G30" s="31"/>
+      <c r="G30" s="32"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="56" t="s">
+      <c r="A31" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="B31" s="56" t="s">
+      <c r="B31" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="C31" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="38" t="s">
+      <c r="E31" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F31" s="31" t="s">
+      <c r="F31" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="G31" s="31"/>
+      <c r="G31" s="32"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="56" t="s">
+      <c r="A32" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="56" t="s">
+      <c r="B32" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="38" t="s">
+      <c r="E32" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F32" s="31" t="s">
+      <c r="F32" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="G32" s="31"/>
+      <c r="G32" s="32"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="56" t="s">
+      <c r="A33" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="56" t="s">
+      <c r="B33" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="31" t="s">
+      <c r="C33" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E33" s="38" t="s">
+      <c r="E33" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F33" s="31" t="s">
+      <c r="F33" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="G33" s="31"/>
+      <c r="G33" s="32"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="56" t="s">
+      <c r="A34" s="57" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="56"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="56"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
+      <c r="A35" s="57"/>
+      <c r="B35" s="57"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="56" t="s">
+      <c r="A36" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="B36" s="56" t="s">
+      <c r="B36" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="D36" s="32"/>
-      <c r="E36" s="38" t="s">
+      <c r="D36" s="33"/>
+      <c r="E36" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="56" t="s">
+      <c r="A37" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="56" t="s">
+      <c r="B37" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="C37" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="32"/>
-      <c r="E37" s="38" t="s">
+      <c r="D37" s="33"/>
+      <c r="E37" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="56" t="s">
+      <c r="A38" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="56" t="s">
+      <c r="B38" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="C38" s="31" t="s">
+      <c r="C38" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="D38" s="32"/>
-      <c r="E38" s="38" t="s">
+      <c r="D38" s="33"/>
+      <c r="E38" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="56" t="s">
+      <c r="A39" s="57" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="56" t="s">
+      <c r="B39" s="57" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="57" t="s">
+      <c r="C39" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="D39" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E39" s="38" t="s">
+      <c r="E39" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F39" s="39" t="s">
+      <c r="F39" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="G39" s="31"/>
+      <c r="G39" s="32"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="56" t="s">
+      <c r="A40" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="56" t="s">
+      <c r="B40" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="C40" s="31" t="s">
+      <c r="C40" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="D40" s="32"/>
-      <c r="E40" s="38" t="s">
+      <c r="D40" s="33"/>
+      <c r="E40" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="56" t="s">
+      <c r="A41" s="57" t="s">
         <v>117</v>
       </c>
-      <c r="B41" s="56" t="s">
+      <c r="B41" s="57" t="s">
         <v>117</v>
       </c>
-      <c r="C41" s="31" t="s">
+      <c r="C41" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="D41" s="32"/>
-      <c r="E41" s="38" t="s">
+      <c r="D41" s="33"/>
+      <c r="E41" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="56" t="s">
+      <c r="A42" s="57" t="s">
         <v>119</v>
       </c>
-      <c r="B42" s="56"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="31"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="60"/>
+      <c r="G42" s="32"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="56" t="s">
+      <c r="A43" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="B43" s="56"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="56" t="s">
+      <c r="A44" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="56" t="s">
+      <c r="B44" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="31" t="s">
+      <c r="C44" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="D44" s="32" t="s">
+      <c r="D44" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E44" s="32" t="s">
+      <c r="E44" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F44" s="31" t="s">
+      <c r="F44" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="G44" s="31"/>
+      <c r="G44" s="32"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="56" t="s">
+      <c r="A45" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="B45" s="56" t="s">
+      <c r="B45" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="C45" s="31" t="s">
+      <c r="C45" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="D45" s="32" t="s">
+      <c r="D45" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E45" s="32" t="s">
+      <c r="E45" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F45" s="31" t="s">
+      <c r="F45" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="G45" s="31"/>
+      <c r="G45" s="32"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="56" t="s">
+      <c r="A46" s="57" t="s">
         <v>126</v>
       </c>
-      <c r="B46" s="56" t="s">
+      <c r="B46" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="C46" s="31" t="s">
+      <c r="C46" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="D46" s="32" t="s">
+      <c r="D46" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="E46" s="32" t="s">
+      <c r="E46" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="F46" s="31" t="s">
+      <c r="F46" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="G46" s="31"/>
+      <c r="G46" s="32"/>
     </row>
     <row r="47" ht="14.65" customHeight="1" spans="1:7">
-      <c r="A47" s="56" t="s">
+      <c r="A47" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="56" t="s">
+      <c r="B47" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="C47" s="31" t="s">
+      <c r="C47" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="D47" s="32" t="s">
+      <c r="D47" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="E47" s="32" t="s">
+      <c r="E47" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="31" t="s">
+      <c r="F47" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="G47" s="31"/>
+      <c r="G47" s="32"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="56" t="s">
+      <c r="A48" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="B48" s="56"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="32"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="31"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="33"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="56" t="s">
+      <c r="A49" s="57" t="s">
         <v>135</v>
       </c>
-      <c r="B49" s="56"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="33"/>
+      <c r="E49" s="33"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="56" t="s">
+      <c r="A50" s="57" t="s">
         <v>136</v>
       </c>
-      <c r="B50" s="56"/>
-      <c r="C50" s="31"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="31"/>
-      <c r="G50" s="31"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="33"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="56" t="s">
+      <c r="A51" s="57" t="s">
         <v>137</v>
       </c>
-      <c r="B51" s="56"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="31"/>
-      <c r="G51" s="31"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="33"/>
+      <c r="E51" s="33"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="56"/>
-      <c r="B52" s="56"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="32"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="31"/>
+      <c r="A52" s="57"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="33"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="56" t="s">
+      <c r="A53" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="B53" s="56" t="s">
+      <c r="B53" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="C53" s="31" t="s">
+      <c r="C53" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="D53" s="32"/>
-      <c r="E53" s="38" t="s">
+      <c r="D53" s="33"/>
+      <c r="E53" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F53" s="59" t="s">
+      <c r="F53" s="60" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="31"/>
+      <c r="G53" s="32"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="56" t="s">
+      <c r="A54" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="B54" s="56" t="s">
+      <c r="B54" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="C54" s="31" t="s">
+      <c r="C54" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="D54" s="32" t="s">
+      <c r="D54" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E54" s="32" t="s">
+      <c r="E54" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F54" s="31" t="s">
+      <c r="F54" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="G54" s="31"/>
+      <c r="G54" s="32"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="56" t="s">
+      <c r="A55" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="B55" s="56" t="s">
+      <c r="B55" s="57" t="s">
         <v>145</v>
       </c>
-      <c r="C55" s="31" t="s">
+      <c r="C55" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="D55" s="32" t="s">
+      <c r="D55" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E55" s="32" t="s">
+      <c r="E55" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F55" s="31" t="s">
+      <c r="F55" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="G55" s="31"/>
+      <c r="G55" s="32"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="56" t="s">
+      <c r="A56" s="57" t="s">
         <v>148</v>
       </c>
-      <c r="D56" s="32"/>
-      <c r="E56" s="32"/>
-      <c r="F56" s="31"/>
-      <c r="G56" s="31"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="33"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="56" t="s">
+      <c r="A57" s="57" t="s">
         <v>149</v>
       </c>
-      <c r="B57" s="56" t="s">
+      <c r="B57" s="57" t="s">
         <v>149</v>
       </c>
-      <c r="C57" s="31" t="s">
+      <c r="C57" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="D57" s="32" t="s">
+      <c r="D57" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E57" s="32" t="s">
+      <c r="E57" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="F57" s="59" t="s">
+      <c r="F57" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="G57" s="31"/>
+      <c r="G57" s="32"/>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="56" t="s">
+      <c r="A58" s="57" t="s">
         <v>152</v>
       </c>
-      <c r="B58" s="56" t="s">
+      <c r="B58" s="57" t="s">
         <v>153</v>
       </c>
-      <c r="C58" s="31" t="s">
+      <c r="C58" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="D58" s="32"/>
-      <c r="E58" s="32" t="s">
+      <c r="D58" s="33"/>
+      <c r="E58" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="F58" s="37" t="s">
+      <c r="F58" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="G58" s="60" t="s">
+      <c r="G58" s="61" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="56" t="s">
+      <c r="A59" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="B59" s="56" t="s">
+      <c r="B59" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="C59" s="31" t="s">
+      <c r="C59" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32" t="s">
+      <c r="D59" s="33"/>
+      <c r="E59" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="F59" s="37" t="s">
+      <c r="F59" s="38" t="s">
         <v>161</v>
       </c>
-      <c r="G59" s="61"/>
+      <c r="G59" s="62"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="56" t="s">
+      <c r="A60" s="57" t="s">
         <v>162</v>
       </c>
-      <c r="B60" s="56" t="s">
+      <c r="B60" s="57" t="s">
         <v>162</v>
       </c>
-      <c r="C60" s="31" t="s">
+      <c r="C60" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="D60" s="32"/>
-      <c r="E60" s="32" t="s">
+      <c r="D60" s="33"/>
+      <c r="E60" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="F60" s="37" t="s">
+      <c r="F60" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="G60" s="61"/>
+      <c r="G60" s="62"/>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="56" t="s">
+      <c r="A61" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="B61" s="56" t="s">
+      <c r="B61" s="57" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="31" t="s">
+      <c r="C61" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="D61" s="32" t="s">
+      <c r="D61" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E61" s="32" t="s">
+      <c r="E61" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="F61" s="37" t="s">
+      <c r="F61" s="38" t="s">
         <v>167</v>
       </c>
-      <c r="G61" s="61"/>
+      <c r="G61" s="62"/>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="56" t="s">
+      <c r="A62" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="B62" s="56" t="s">
+      <c r="B62" s="57" t="s">
         <v>168</v>
       </c>
-      <c r="C62" s="31" t="s">
+      <c r="C62" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="D62" s="32" t="s">
+      <c r="D62" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E62" s="32" t="s">
+      <c r="E62" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="F62" s="37" t="s">
+      <c r="F62" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="G62" s="62"/>
+      <c r="G62" s="63"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="56" t="s">
+      <c r="A63" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="56"/>
-      <c r="C63" s="31"/>
-      <c r="D63" s="32"/>
-      <c r="E63" s="32"/>
-      <c r="F63" s="31"/>
-      <c r="G63" s="31"/>
+      <c r="B63" s="57"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="32"/>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="56" t="s">
+      <c r="A64" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="B64" s="56"/>
-      <c r="C64" s="31"/>
-      <c r="D64" s="32"/>
-      <c r="E64" s="32"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
+      <c r="B64" s="57"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="33"/>
+      <c r="E64" s="33"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="56" t="s">
+      <c r="A65" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="B65" s="56" t="s">
+      <c r="B65" s="57" t="s">
         <v>135</v>
       </c>
-      <c r="C65" s="31" t="s">
+      <c r="C65" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="D65" s="32" t="s">
+      <c r="D65" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E65" s="32" t="s">
+      <c r="E65" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F65" s="31" t="s">
+      <c r="F65" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="G65" s="31"/>
+      <c r="G65" s="32"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="56" t="s">
+      <c r="A66" s="57" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="56"/>
-      <c r="C66" s="31"/>
-      <c r="D66" s="32"/>
-      <c r="E66" s="32"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="31"/>
+      <c r="B66" s="57"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="33"/>
+      <c r="E66" s="33"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="32"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="56" t="s">
+      <c r="A67" s="57" t="s">
         <v>153</v>
       </c>
-      <c r="B67" s="56" t="s">
+      <c r="B67" s="57" t="s">
         <v>136</v>
       </c>
-      <c r="C67" s="31" t="s">
+      <c r="C67" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="D67" s="32" t="s">
+      <c r="D67" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E67" s="32" t="s">
+      <c r="E67" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F67" s="31" t="s">
+      <c r="F67" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="G67" s="31"/>
+      <c r="G67" s="32"/>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="56" t="s">
+      <c r="A68" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="B68" s="56" t="s">
+      <c r="B68" s="57" t="s">
         <v>137</v>
       </c>
-      <c r="C68" s="31" t="s">
+      <c r="C68" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="D68" s="32" t="s">
+      <c r="D68" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E68" s="32" t="s">
+      <c r="E68" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F68" s="31" t="s">
+      <c r="F68" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="G68" s="31"/>
+      <c r="G68" s="32"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="56"/>
-      <c r="B69" s="56"/>
-      <c r="C69" s="31"/>
-      <c r="D69" s="32"/>
-      <c r="E69" s="32"/>
-      <c r="F69" s="31"/>
-      <c r="G69" s="31"/>
+      <c r="A69" s="57"/>
+      <c r="B69" s="57"/>
+      <c r="C69" s="32"/>
+      <c r="D69" s="33"/>
+      <c r="E69" s="33"/>
+      <c r="F69" s="32"/>
+      <c r="G69" s="32"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="56" t="s">
+      <c r="A70" s="57" t="s">
         <v>177</v>
       </c>
-      <c r="B70" s="56" t="s">
+      <c r="B70" s="57" t="s">
         <v>178</v>
       </c>
-      <c r="C70" s="31" t="s">
+      <c r="C70" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="D70" s="32" t="s">
+      <c r="D70" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E70" s="32" t="s">
+      <c r="E70" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="F70" s="31" t="s">
+      <c r="F70" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="G70" s="31" t="s">
+      <c r="G70" s="32" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="56" t="s">
+      <c r="A71" s="57" t="s">
         <v>182</v>
       </c>
-      <c r="B71" s="56" t="s">
+      <c r="B71" s="57" t="s">
         <v>183</v>
       </c>
-      <c r="C71" s="31" t="s">
+      <c r="C71" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="D71" s="32" t="s">
+      <c r="D71" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E71" s="32" t="s">
+      <c r="E71" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="F71" s="31" t="s">
+      <c r="F71" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="G71" s="31" t="s">
+      <c r="G71" s="32" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="56" t="s">
+      <c r="A72" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="B72" s="56" t="s">
+      <c r="B72" s="57" t="s">
         <v>186</v>
       </c>
-      <c r="C72" s="31" t="s">
+      <c r="C72" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="D72" s="32" t="s">
+      <c r="D72" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="E72" s="32" t="s">
+      <c r="E72" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="31" t="s">
+      <c r="F72" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="G72" s="31"/>
+      <c r="G72" s="32"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="56" t="s">
+      <c r="A73" s="57" t="s">
         <v>189</v>
       </c>
-      <c r="B73" s="56" t="s">
+      <c r="B73" s="57" t="s">
         <v>189</v>
       </c>
-      <c r="C73" s="31" t="s">
+      <c r="C73" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="D73" s="32" t="s">
+      <c r="D73" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="E73" s="32" t="s">
+      <c r="E73" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="F73" s="31" t="s">
+      <c r="F73" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="G73" s="31"/>
+      <c r="G73" s="32"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="56" t="s">
+      <c r="A74" s="57" t="s">
         <v>191</v>
       </c>
-      <c r="B74" s="56" t="s">
+      <c r="B74" s="57" t="s">
         <v>191</v>
       </c>
-      <c r="C74" s="31" t="s">
+      <c r="C74" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="D74" s="32" t="s">
+      <c r="D74" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E74" s="38" t="s">
+      <c r="E74" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F74" s="31" t="s">
+      <c r="F74" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="G74" s="31"/>
+      <c r="G74" s="32"/>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="56" t="s">
+      <c r="A75" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="B75" s="56" t="s">
+      <c r="B75" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="C75" s="31" t="s">
+      <c r="C75" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="D75" s="32"/>
-      <c r="E75" s="32" t="s">
+      <c r="D75" s="33"/>
+      <c r="E75" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="F75" s="37" t="s">
+      <c r="F75" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="G75" s="59" t="s">
+      <c r="G75" s="60" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="56" t="s">
+      <c r="A76" s="57" t="s">
         <v>197</v>
       </c>
-      <c r="B76" s="56" t="s">
+      <c r="B76" s="57" t="s">
         <v>197</v>
       </c>
-      <c r="C76" s="31" t="s">
+      <c r="C76" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="D76" s="32" t="s">
+      <c r="D76" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E76" s="32" t="s">
+      <c r="E76" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="F76" s="31" t="s">
+      <c r="F76" s="32" t="s">
         <v>199</v>
       </c>
-      <c r="G76" s="31"/>
+      <c r="G76" s="32"/>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="56" t="s">
+      <c r="A77" s="57" t="s">
         <v>200</v>
       </c>
-      <c r="B77" s="56" t="s">
+      <c r="B77" s="57" t="s">
         <v>200</v>
       </c>
-      <c r="C77" s="31" t="s">
+      <c r="C77" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="D77" s="32" t="s">
+      <c r="D77" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E77" s="32" t="s">
+      <c r="E77" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="F77" s="31" t="s">
+      <c r="F77" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="G77" s="31"/>
+      <c r="G77" s="32"/>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="56" t="s">
+      <c r="A78" s="57" t="s">
         <v>203</v>
       </c>
-      <c r="B78" s="56" t="s">
+      <c r="B78" s="57" t="s">
         <v>80</v>
       </c>
-      <c r="C78" s="31" t="s">
+      <c r="C78" s="32" t="s">
         <v>204</v>
       </c>
-      <c r="D78" s="32" t="s">
+      <c r="D78" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E78" s="32" t="s">
+      <c r="E78" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="F78" s="31" t="s">
+      <c r="F78" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="G78" s="31"/>
+      <c r="G78" s="32"/>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="56" t="s">
+      <c r="A79" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="B79" s="56" t="s">
+      <c r="B79" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="C79" s="31" t="s">
+      <c r="C79" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="D79" s="32" t="s">
+      <c r="D79" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E79" s="32" t="s">
+      <c r="E79" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="F79" s="31" t="s">
+      <c r="F79" s="32" t="s">
         <v>208</v>
       </c>
-      <c r="G79" s="31"/>
+      <c r="G79" s="32"/>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="56" t="s">
+      <c r="A80" s="57" t="s">
         <v>209</v>
       </c>
-      <c r="B80" s="56" t="s">
+      <c r="B80" s="57" t="s">
         <v>210</v>
       </c>
-      <c r="C80" s="31" t="s">
+      <c r="C80" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="D80" s="32" t="s">
+      <c r="D80" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E80" s="32" t="s">
+      <c r="E80" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="F80" s="31" t="s">
+      <c r="F80" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="G80" s="31"/>
+      <c r="G80" s="32"/>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" s="56" t="s">
+      <c r="A81" s="57" t="s">
         <v>210</v>
       </c>
-      <c r="B81" s="56" t="s">
+      <c r="B81" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="C81" s="31" t="s">
+      <c r="C81" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="D81" s="32" t="s">
+      <c r="D81" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="E81" s="32" t="s">
+      <c r="E81" s="33" t="s">
         <v>215</v>
       </c>
-      <c r="F81" s="31" t="s">
+      <c r="F81" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="G81" s="31"/>
+      <c r="G81" s="32"/>
     </row>
     <row r="82" spans="1:7">
-      <c r="A82" s="56" t="s">
+      <c r="A82" s="57" t="s">
         <v>217</v>
       </c>
-      <c r="B82" s="56" t="s">
+      <c r="B82" s="57" t="s">
         <v>218</v>
       </c>
-      <c r="C82" s="31" t="s">
+      <c r="C82" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="D82" s="32" t="s">
+      <c r="D82" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="E82" s="32" t="s">
+      <c r="E82" s="33" t="s">
         <v>215</v>
       </c>
-      <c r="F82" s="31" t="s">
+      <c r="F82" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="G82" s="31"/>
+      <c r="G82" s="32"/>
     </row>
     <row r="83" spans="1:7">
-      <c r="A83" s="56" t="s">
+      <c r="A83" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="B83" s="56" t="s">
+      <c r="B83" s="57" t="s">
         <v>220</v>
       </c>
-      <c r="C83" s="37" t="s">
+      <c r="C83" s="38" t="s">
         <v>221</v>
       </c>
-      <c r="D83" s="32" t="s">
+      <c r="D83" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="E83" s="32" t="s">
+      <c r="E83" s="33" t="s">
         <v>215</v>
       </c>
-      <c r="F83" s="31" t="s">
+      <c r="F83" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="G83" s="31" t="s">
+      <c r="G83" s="32" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="56" t="s">
+      <c r="A84" s="57" t="s">
         <v>223</v>
       </c>
-      <c r="B84" s="56" t="s">
+      <c r="B84" s="57" t="s">
         <v>224</v>
       </c>
-      <c r="C84" s="37" t="s">
+      <c r="C84" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="D84" s="32" t="s">
+      <c r="D84" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="E84" s="32" t="s">
+      <c r="E84" s="33" t="s">
         <v>215</v>
       </c>
-      <c r="F84" s="31" t="s">
+      <c r="F84" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="G84" s="31" t="s">
+      <c r="G84" s="32" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="56" t="s">
+      <c r="A85" s="57" t="s">
         <v>227</v>
       </c>
-      <c r="B85" s="56" t="s">
+      <c r="B85" s="57" t="s">
         <v>227</v>
       </c>
-      <c r="C85" s="31" t="s">
+      <c r="C85" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="D85" s="32" t="s">
+      <c r="D85" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E85" s="38" t="s">
+      <c r="E85" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="F85" s="31" t="s">
+      <c r="F85" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="G85" s="31"/>
+      <c r="G85" s="32"/>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="56"/>
-      <c r="B86" s="56"/>
-      <c r="C86" s="31"/>
-      <c r="D86" s="32"/>
-      <c r="E86" s="32"/>
-      <c r="F86" s="31"/>
-      <c r="G86" s="31"/>
+      <c r="A86" s="57"/>
+      <c r="B86" s="57"/>
+      <c r="C86" s="32"/>
+      <c r="D86" s="33"/>
+      <c r="E86" s="33"/>
+      <c r="F86" s="32"/>
+      <c r="G86" s="32"/>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" s="56" t="s">
+      <c r="A87" s="57" t="s">
         <v>230</v>
       </c>
-      <c r="B87" s="56"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="32"/>
-      <c r="E87" s="32"/>
-      <c r="F87" s="31"/>
-      <c r="G87" s="31"/>
+      <c r="B87" s="57"/>
+      <c r="C87" s="32"/>
+      <c r="D87" s="33"/>
+      <c r="E87" s="33"/>
+      <c r="F87" s="32"/>
+      <c r="G87" s="32"/>
     </row>
     <row r="88" spans="1:7">
-      <c r="A88" s="56" t="s">
+      <c r="A88" s="57" t="s">
         <v>231</v>
       </c>
-      <c r="B88" s="56"/>
-      <c r="C88" s="31"/>
-      <c r="D88" s="32"/>
-      <c r="E88" s="32"/>
-      <c r="F88" s="31"/>
-      <c r="G88" s="31"/>
+      <c r="B88" s="57"/>
+      <c r="C88" s="32"/>
+      <c r="D88" s="33"/>
+      <c r="E88" s="33"/>
+      <c r="F88" s="32"/>
+      <c r="G88" s="32"/>
     </row>
     <row r="91" spans="1:7">
-      <c r="A91" s="56" t="s">
+      <c r="A91" s="57" t="s">
         <v>232</v>
       </c>
-      <c r="B91" s="56" t="s">
+      <c r="B91" s="57" t="s">
         <v>233</v>
       </c>
-      <c r="C91" s="31" t="s">
+      <c r="C91" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="D91" s="32" t="s">
+      <c r="D91" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E91" s="32" t="s">
+      <c r="E91" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="F91" s="31" t="s">
+      <c r="F91" s="32" t="s">
         <v>235</v>
       </c>
       <c r="G91" t="s">
@@ -4839,22 +4843,22 @@
       </c>
     </row>
     <row r="92" spans="1:7">
-      <c r="A92" s="56" t="s">
+      <c r="A92" s="57" t="s">
         <v>232</v>
       </c>
-      <c r="B92" s="56" t="s">
+      <c r="B92" s="57" t="s">
         <v>237</v>
       </c>
-      <c r="C92" s="31" t="s">
+      <c r="C92" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="D92" s="32" t="s">
+      <c r="D92" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E92" s="32" t="s">
+      <c r="E92" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="F92" s="31" t="s">
+      <c r="F92" s="32" t="s">
         <v>235</v>
       </c>
       <c r="G92" t="s">
@@ -4862,7 +4866,7 @@
       </c>
     </row>
     <row r="93" spans="1:7">
-      <c r="D93" s="28" t="s">
+      <c r="D93" s="29" t="s">
         <v>240</v>
       </c>
     </row>
@@ -4886,7 +4890,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="28.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="18.2685185185185" style="28" customWidth="1"/>
+    <col min="3" max="3" width="18.2685185185185" style="29" customWidth="1"/>
     <col min="4" max="4" width="17.0648148148148" customWidth="1"/>
     <col min="5" max="5" width="72" customWidth="1"/>
     <col min="6" max="6" width="23.462962962963" customWidth="1"/>
@@ -4894,1362 +4898,1362 @@
     <col min="8" max="8" width="31.6018518518519" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="26" customFormat="1" ht="28.5" customHeight="1" spans="1:7">
-      <c r="A1" s="29" t="s">
+    <row r="1" s="27" customFormat="1" ht="28.5" customHeight="1" spans="1:7">
+      <c r="A1" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="31" t="s">
         <v>242</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="30" t="s">
         <v>244</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="30" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="32" t="s">
         <v>245</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="32" t="s">
         <v>248</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-    </row>
-    <row r="6" s="27" customFormat="1" spans="1:7">
-      <c r="A6" s="33" t="s">
+      <c r="C5" s="33"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+    </row>
+    <row r="6" s="28" customFormat="1" spans="1:7">
+      <c r="A6" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="36" t="s">
         <v>249</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33" t="s">
+      <c r="D6" s="34"/>
+      <c r="E6" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-    </row>
-    <row r="7" s="27" customFormat="1" spans="1:7">
-      <c r="A7" s="33" t="s">
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+    </row>
+    <row r="7" s="28" customFormat="1" spans="1:7">
+      <c r="A7" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="36" t="s">
         <v>249</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33" t="s">
+      <c r="D7" s="34"/>
+      <c r="E7" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-    </row>
-    <row r="8" s="27" customFormat="1" spans="1:7">
-      <c r="A8" s="33" t="s">
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+    </row>
+    <row r="8" s="28" customFormat="1" spans="1:7">
+      <c r="A8" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="36" t="s">
         <v>249</v>
       </c>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33" t="s">
+      <c r="D8" s="34"/>
+      <c r="E8" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-    </row>
-    <row r="9" s="27" customFormat="1" spans="1:7">
-      <c r="A9" s="33" t="s">
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+    </row>
+    <row r="9" s="28" customFormat="1" spans="1:7">
+      <c r="A9" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="36" t="s">
         <v>249</v>
       </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33" t="s">
+      <c r="D9" s="34"/>
+      <c r="E9" s="34" t="s">
         <v>250</v>
       </c>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="37" t="s">
+      <c r="B10" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="38" t="s">
         <v>251</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37" t="s">
+      <c r="F10" s="38"/>
+      <c r="G10" s="38" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="C12" s="32"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37" t="s">
+      <c r="D13" s="38"/>
+      <c r="E13" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="F13" s="37"/>
-      <c r="G13" s="39" t="s">
+      <c r="F13" s="38"/>
+      <c r="G13" s="40" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="38" t="s">
         <v>258</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37" t="s">
+      <c r="D14" s="38"/>
+      <c r="E14" s="38" t="s">
         <v>259</v>
       </c>
-      <c r="F14" s="37"/>
-      <c r="G14" s="39" t="s">
+      <c r="F14" s="38"/>
+      <c r="G14" s="40" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="32" t="s">
         <v>261</v>
       </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36" t="s">
+      <c r="D17" s="37"/>
+      <c r="E17" s="37" t="s">
         <v>263</v>
       </c>
-      <c r="F17" s="37"/>
-      <c r="G17" s="39" t="s">
+      <c r="F17" s="38"/>
+      <c r="G17" s="40" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="33" t="s">
+      <c r="A19" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="35" t="s">
+      <c r="C19" s="36" t="s">
         <v>249</v>
       </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33" t="s">
+      <c r="D19" s="34"/>
+      <c r="E19" s="34" t="s">
         <v>265</v>
       </c>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="36" t="s">
+      <c r="A20" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36" t="s">
+      <c r="D20" s="37"/>
+      <c r="E20" s="37" t="s">
         <v>266</v>
       </c>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37" t="s">
+      <c r="F20" s="38"/>
+      <c r="G20" s="38" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36" t="s">
+      <c r="D21" s="37"/>
+      <c r="E21" s="37" t="s">
         <v>268</v>
       </c>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37" t="s">
+      <c r="F21" s="38"/>
+      <c r="G21" s="38" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="37" t="s">
+      <c r="B22" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37" t="s">
+      <c r="C22" s="39"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="F22" s="42" t="s">
+      <c r="F22" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="G22" s="37"/>
+      <c r="G22" s="38"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="38"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37" t="s">
+      <c r="C23" s="39"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="F23" s="43"/>
-      <c r="G23" s="37"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="38"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="39" t="s">
+      <c r="A24" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36" t="s">
+      <c r="D24" s="37"/>
+      <c r="E24" s="37" t="s">
         <v>272</v>
       </c>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36" t="s">
+      <c r="D25" s="37"/>
+      <c r="E25" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="F25" s="37"/>
-      <c r="G25" s="39" t="s">
+      <c r="F25" s="38"/>
+      <c r="G25" s="40" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="32" t="s">
         <v>274</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="33" t="s">
         <v>271</v>
       </c>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31" t="s">
+      <c r="D26" s="32"/>
+      <c r="E26" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31" t="s">
+      <c r="F26" s="32"/>
+      <c r="G26" s="32" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="33" t="s">
+      <c r="A27" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="35" t="s">
+      <c r="C27" s="36" t="s">
         <v>271</v>
       </c>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33" t="s">
+      <c r="D27" s="34"/>
+      <c r="E27" s="34" t="s">
         <v>277</v>
       </c>
-      <c r="F27" s="37"/>
-      <c r="G27" s="39" t="s">
+      <c r="F27" s="38"/>
+      <c r="G27" s="40" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="B28" s="36" t="s">
+      <c r="B28" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="40" t="s">
+      <c r="C28" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36" t="s">
+      <c r="D28" s="37"/>
+      <c r="E28" s="37" t="s">
         <v>278</v>
       </c>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37" t="s">
+      <c r="F28" s="38"/>
+      <c r="G28" s="38" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="36" t="s">
+      <c r="A29" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="40" t="s">
+      <c r="C29" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36" t="s">
+      <c r="D29" s="37"/>
+      <c r="E29" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="37" t="s">
+      <c r="A30" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37" t="s">
+      <c r="D30" s="38"/>
+      <c r="E30" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="F30" s="44"/>
-      <c r="G30" s="39" t="s">
+      <c r="F30" s="45"/>
+      <c r="G30" s="40" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="C31" s="32"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="31"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="32"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="31" t="s">
+      <c r="A32" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="32" t="s">
         <v>282</v>
       </c>
-      <c r="C32" s="32"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="31"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="32"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="32" t="s">
         <v>283</v>
       </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="31"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="32"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="31" t="s">
+      <c r="B34" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="31"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="32"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="31"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="31"/>
+      <c r="A35" s="32"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="32"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="B36" s="31" t="s">
+      <c r="B36" s="32" t="s">
         <v>285</v>
       </c>
-      <c r="C36" s="32"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="31"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="32"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="31" t="s">
+      <c r="B37" s="32" t="s">
         <v>286</v>
       </c>
-      <c r="C37" s="32"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="31"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="32"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="31" t="s">
+      <c r="B38" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="C38" s="32"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="31"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="32"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="31" t="s">
+      <c r="A39" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="31" t="s">
+      <c r="B39" s="32" t="s">
         <v>288</v>
       </c>
-      <c r="C39" s="32"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="31"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="32"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="37" t="s">
+      <c r="A40" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="37" t="s">
+      <c r="B40" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="C40" s="38"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="39" t="s">
+      <c r="C40" s="39"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="47"/>
+      <c r="G40" s="40" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="B41" s="31" t="s">
+      <c r="B41" s="32" t="s">
         <v>290</v>
       </c>
-      <c r="C41" s="32"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="45"/>
-      <c r="G41" s="31"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="46"/>
+      <c r="G41" s="32"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="B42" s="31" t="s">
+      <c r="B42" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="C42" s="32"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="45"/>
-      <c r="G42" s="31"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="32"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="31" t="s">
+      <c r="A43" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="B43" s="31" t="s">
+      <c r="B43" s="32" t="s">
         <v>292</v>
       </c>
-      <c r="C43" s="32"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="45"/>
-      <c r="G43" s="31"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="46"/>
+      <c r="G43" s="32"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="36" t="s">
+      <c r="A44" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="36" t="s">
+      <c r="B44" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="40" t="s">
+      <c r="C44" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36" t="s">
+      <c r="D44" s="37"/>
+      <c r="E44" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="F44" s="46"/>
-      <c r="G44" s="37" t="s">
+      <c r="F44" s="47"/>
+      <c r="G44" s="38" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="36" t="s">
+      <c r="A45" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="B45" s="36" t="s">
+      <c r="B45" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="C45" s="40" t="s">
+      <c r="C45" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="D45" s="36"/>
-      <c r="E45" s="36" t="s">
+      <c r="D45" s="37"/>
+      <c r="E45" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="F45" s="37"/>
-      <c r="G45" s="37"/>
+      <c r="F45" s="38"/>
+      <c r="G45" s="38"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="B46" s="36" t="s">
+      <c r="B46" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="C46" s="40" t="s">
+      <c r="C46" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36" t="s">
+      <c r="D46" s="37"/>
+      <c r="E46" s="37" t="s">
         <v>295</v>
       </c>
-      <c r="F46" s="47" t="s">
+      <c r="F46" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="G46" s="37" t="s">
+      <c r="G46" s="38" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="47" ht="14.65" customHeight="1" spans="1:7">
-      <c r="A47" s="36" t="s">
+      <c r="A47" s="37" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="36" t="s">
+      <c r="B47" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="C47" s="40" t="s">
+      <c r="C47" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="D47" s="36"/>
-      <c r="E47" s="36" t="s">
+      <c r="D47" s="37"/>
+      <c r="E47" s="37" t="s">
         <v>295</v>
       </c>
-      <c r="F47" s="48"/>
-      <c r="G47" s="37"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="38"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="37" t="s">
+      <c r="A48" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="B48" s="37" t="s">
+      <c r="B48" s="38" t="s">
         <v>297</v>
       </c>
-      <c r="C48" s="38" t="s">
+      <c r="C48" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37" t="s">
+      <c r="D48" s="38"/>
+      <c r="E48" s="38" t="s">
         <v>298</v>
       </c>
-      <c r="F48" s="37"/>
-      <c r="G48" s="39" t="s">
+      <c r="F48" s="38"/>
+      <c r="G48" s="40" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="37" t="s">
+      <c r="A49" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="B49" s="37" t="s">
+      <c r="B49" s="38" t="s">
         <v>300</v>
       </c>
-      <c r="C49" s="38" t="s">
+      <c r="C49" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D49" s="37"/>
-      <c r="E49" s="37" t="s">
+      <c r="D49" s="38"/>
+      <c r="E49" s="38" t="s">
         <v>298</v>
       </c>
-      <c r="F49" s="37"/>
-      <c r="G49" s="39"/>
+      <c r="F49" s="38"/>
+      <c r="G49" s="40"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="37" t="s">
+      <c r="A50" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B50" s="37" t="s">
+      <c r="B50" s="38" t="s">
         <v>301</v>
       </c>
-      <c r="C50" s="38" t="s">
+      <c r="C50" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37" t="s">
+      <c r="D50" s="38"/>
+      <c r="E50" s="38" t="s">
         <v>302</v>
       </c>
-      <c r="F50" s="37"/>
-      <c r="G50" s="39"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="40"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="37" t="s">
+      <c r="A51" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="B51" s="37" t="s">
+      <c r="B51" s="38" t="s">
         <v>303</v>
       </c>
-      <c r="C51" s="38" t="s">
+      <c r="C51" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D51" s="37"/>
-      <c r="E51" s="37" t="s">
+      <c r="D51" s="38"/>
+      <c r="E51" s="38" t="s">
         <v>304</v>
       </c>
-      <c r="F51" s="37"/>
-      <c r="G51" s="39"/>
+      <c r="F51" s="38"/>
+      <c r="G51" s="40"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="31"/>
-      <c r="B52" s="31"/>
-      <c r="C52" s="32"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="31"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="33"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="31" t="s">
+      <c r="A53" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="B53" s="31" t="s">
+      <c r="B53" s="32" t="s">
         <v>305</v>
       </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="31" t="s">
+      <c r="A54" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="B54" s="31" t="s">
+      <c r="B54" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="C54" s="32"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="31"/>
-      <c r="G54" s="31"/>
+      <c r="C54" s="33"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="31" t="s">
+      <c r="A55" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="B55" s="31" t="s">
+      <c r="B55" s="32" t="s">
         <v>307</v>
       </c>
-      <c r="C55" s="32"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="31"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="31" t="s">
+      <c r="A56" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="B56" s="31" t="s">
+      <c r="B56" s="32" t="s">
         <v>308</v>
       </c>
-      <c r="C56" s="32"/>
-      <c r="D56" s="31"/>
-      <c r="E56" s="31"/>
-      <c r="F56" s="31"/>
-      <c r="G56" s="31"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="36" t="s">
+      <c r="A57" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="B57" s="36" t="s">
+      <c r="B57" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="C57" s="40" t="s">
+      <c r="C57" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="D57" s="36"/>
-      <c r="E57" s="36" t="s">
+      <c r="D57" s="37"/>
+      <c r="E57" s="37" t="s">
         <v>309</v>
       </c>
-      <c r="F57" s="37"/>
-      <c r="G57" s="37" t="s">
+      <c r="F57" s="38"/>
+      <c r="G57" s="38" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="31" t="s">
+      <c r="A58" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="B58" s="31" t="s">
+      <c r="B58" s="32" t="s">
         <v>311</v>
       </c>
-      <c r="C58" s="32"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="31"/>
+      <c r="C58" s="33"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="31" t="s">
+      <c r="A59" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="B59" s="31" t="s">
+      <c r="B59" s="32" t="s">
         <v>312</v>
       </c>
-      <c r="C59" s="32"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="31"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="31" t="s">
+      <c r="A60" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="B60" s="31" t="s">
+      <c r="B60" s="32" t="s">
         <v>313</v>
       </c>
-      <c r="C60" s="32"/>
-      <c r="D60" s="31"/>
-      <c r="E60" s="31"/>
-      <c r="F60" s="31"/>
-      <c r="G60" s="31"/>
+      <c r="C60" s="33"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="39" t="s">
+      <c r="A61" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="B61" s="39" t="s">
+      <c r="B61" s="40" t="s">
         <v>314</v>
       </c>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="49" t="s">
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="50" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="39" t="s">
+      <c r="A62" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="B62" s="39" t="s">
+      <c r="B62" s="40" t="s">
         <v>316</v>
       </c>
-      <c r="C62" s="32"/>
-      <c r="D62" s="31"/>
-      <c r="E62" s="31"/>
-      <c r="F62" s="31"/>
-      <c r="G62" s="50"/>
+      <c r="C62" s="33"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="32"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="51"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="31" t="s">
+      <c r="A63" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="31" t="s">
+      <c r="B63" s="32" t="s">
         <v>317</v>
       </c>
-      <c r="C63" s="32"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="31"/>
-      <c r="F63" s="31"/>
-      <c r="G63" s="31"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="32"/>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="31" t="s">
+      <c r="A64" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="B64" s="31" t="s">
+      <c r="B64" s="32" t="s">
         <v>318</v>
       </c>
-      <c r="C64" s="32"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="37" t="s">
+      <c r="A65" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="B65" s="37" t="s">
+      <c r="B65" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="C65" s="38" t="s">
+      <c r="C65" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="D65" s="37"/>
-      <c r="E65" s="37" t="s">
+      <c r="D65" s="38"/>
+      <c r="E65" s="38" t="s">
         <v>319</v>
       </c>
-      <c r="F65" s="37"/>
-      <c r="G65" s="39" t="s">
+      <c r="F65" s="38"/>
+      <c r="G65" s="40" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="31" t="s">
+      <c r="A66" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="31" t="s">
+      <c r="B66" s="32" t="s">
         <v>320</v>
       </c>
-      <c r="C66" s="32"/>
-      <c r="D66" s="31"/>
-      <c r="E66" s="31"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="31"/>
+      <c r="C66" s="33"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="32"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="32"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="36" t="s">
+      <c r="A67" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="B67" s="36" t="s">
+      <c r="B67" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="C67" s="40" t="s">
+      <c r="C67" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="D67" s="36"/>
-      <c r="E67" s="36" t="s">
+      <c r="D67" s="37"/>
+      <c r="E67" s="37" t="s">
         <v>321</v>
       </c>
-      <c r="F67" s="37" t="s">
+      <c r="F67" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="G67" s="37" t="s">
+      <c r="G67" s="38" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="36" t="s">
+      <c r="A68" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="B68" s="36" t="s">
+      <c r="B68" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="C68" s="40" t="s">
+      <c r="C68" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="D68" s="36"/>
-      <c r="E68" s="36" t="s">
+      <c r="D68" s="37"/>
+      <c r="E68" s="37" t="s">
         <v>321</v>
       </c>
-      <c r="F68" s="37" t="s">
+      <c r="F68" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="G68" s="37" t="s">
+      <c r="G68" s="38" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="31"/>
-      <c r="B69" s="31"/>
-      <c r="C69" s="32"/>
-      <c r="D69" s="31"/>
-      <c r="E69" s="31"/>
-      <c r="F69" s="31"/>
-      <c r="G69" s="31"/>
+      <c r="A69" s="32"/>
+      <c r="B69" s="32"/>
+      <c r="C69" s="33"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="32"/>
+      <c r="F69" s="32"/>
+      <c r="G69" s="32"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="36" t="s">
+      <c r="A70" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="B70" s="36" t="s">
+      <c r="B70" s="37" t="s">
         <v>179</v>
       </c>
-      <c r="C70" s="40"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36" t="s">
+      <c r="C70" s="41"/>
+      <c r="D70" s="37"/>
+      <c r="E70" s="37" t="s">
         <v>325</v>
       </c>
-      <c r="F70" s="37"/>
-      <c r="G70" s="39" t="s">
+      <c r="F70" s="38"/>
+      <c r="G70" s="40" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="36" t="s">
+      <c r="A71" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="B71" s="36" t="s">
+      <c r="B71" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="C71" s="40"/>
-      <c r="D71" s="36"/>
-      <c r="E71" s="36" t="s">
+      <c r="C71" s="41"/>
+      <c r="D71" s="37"/>
+      <c r="E71" s="37" t="s">
         <v>326</v>
       </c>
-      <c r="F71" s="37"/>
-      <c r="G71" s="39" t="s">
+      <c r="F71" s="38"/>
+      <c r="G71" s="40" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="36" t="s">
+      <c r="A72" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="B72" s="36" t="s">
+      <c r="B72" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="C72" s="40" t="s">
+      <c r="C72" s="41" t="s">
         <v>242</v>
       </c>
-      <c r="D72" s="36"/>
-      <c r="E72" s="36" t="s">
+      <c r="D72" s="37"/>
+      <c r="E72" s="37" t="s">
         <v>327</v>
       </c>
-      <c r="F72" s="37"/>
-      <c r="G72" s="37"/>
+      <c r="F72" s="38"/>
+      <c r="G72" s="38"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="36" t="s">
+      <c r="A73" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="B73" s="36" t="s">
+      <c r="B73" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="C73" s="40" t="s">
+      <c r="C73" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="D73" s="36"/>
-      <c r="E73" s="36" t="s">
+      <c r="D73" s="37"/>
+      <c r="E73" s="37" t="s">
         <v>327</v>
       </c>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
+      <c r="F73" s="38"/>
+      <c r="G73" s="38"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="37" t="s">
+      <c r="A74" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="B74" s="37" t="s">
+      <c r="B74" s="38" t="s">
         <v>328</v>
       </c>
-      <c r="C74" s="38" t="s">
+      <c r="C74" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D74" s="37"/>
-      <c r="E74" s="37" t="s">
+      <c r="D74" s="38"/>
+      <c r="E74" s="38" t="s">
         <v>329</v>
       </c>
-      <c r="F74" s="37"/>
-      <c r="G74" s="39" t="s">
+      <c r="F74" s="38"/>
+      <c r="G74" s="40" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="37" t="s">
+      <c r="A75" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="B75" s="37" t="s">
+      <c r="B75" s="38" t="s">
         <v>331</v>
       </c>
-      <c r="C75" s="38" t="s">
+      <c r="C75" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37" t="s">
+      <c r="D75" s="38"/>
+      <c r="E75" s="38" t="s">
         <v>332</v>
       </c>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
+      <c r="F75" s="38"/>
+      <c r="G75" s="38"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="37" t="s">
+      <c r="A76" s="38" t="s">
         <v>197</v>
       </c>
-      <c r="B76" s="37" t="s">
+      <c r="B76" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="C76" s="38" t="s">
+      <c r="C76" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37" t="s">
+      <c r="D76" s="38"/>
+      <c r="E76" s="38" t="s">
         <v>333</v>
       </c>
-      <c r="F76" s="37"/>
-      <c r="G76" s="39" t="s">
+      <c r="F76" s="38"/>
+      <c r="G76" s="40" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="37" t="s">
+      <c r="A77" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="B77" s="37" t="s">
+      <c r="B77" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="C77" s="38"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="37"/>
-      <c r="F77" s="37"/>
-      <c r="G77" s="39" t="s">
+      <c r="C77" s="39"/>
+      <c r="D77" s="38"/>
+      <c r="E77" s="38"/>
+      <c r="F77" s="38"/>
+      <c r="G77" s="40" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="37" t="s">
+      <c r="A78" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="B78" s="37" t="s">
+      <c r="B78" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="C78" s="38"/>
-      <c r="D78" s="37"/>
-      <c r="E78" s="37"/>
-      <c r="F78" s="37"/>
-      <c r="G78" s="39" t="s">
+      <c r="C78" s="39"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="38"/>
+      <c r="G78" s="40" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="37" t="s">
+      <c r="A79" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="B79" s="37" t="s">
+      <c r="B79" s="38" t="s">
         <v>335</v>
       </c>
-      <c r="C79" s="38" t="s">
+      <c r="C79" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="D79" s="37"/>
-      <c r="E79" s="37" t="s">
+      <c r="D79" s="38"/>
+      <c r="E79" s="38" t="s">
         <v>336</v>
       </c>
-      <c r="F79" s="37"/>
-      <c r="G79" s="39" t="s">
+      <c r="F79" s="38"/>
+      <c r="G79" s="40" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="31" t="s">
+      <c r="A80" s="32" t="s">
         <v>209</v>
       </c>
-      <c r="B80" s="31" t="s">
+      <c r="B80" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="C80" s="32"/>
-      <c r="D80" s="31"/>
-      <c r="E80" s="31"/>
-      <c r="F80" s="31"/>
-      <c r="G80" s="31" t="s">
+      <c r="C80" s="33"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="32"/>
+      <c r="F80" s="32"/>
+      <c r="G80" s="32" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" s="36" t="s">
+      <c r="A81" s="37" t="s">
         <v>210</v>
       </c>
-      <c r="B81" s="36" t="s">
+      <c r="B81" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="C81" s="40" t="s">
+      <c r="C81" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="D81" s="36"/>
-      <c r="E81" s="36" t="s">
+      <c r="D81" s="37"/>
+      <c r="E81" s="37" t="s">
         <v>338</v>
       </c>
-      <c r="F81" s="36"/>
-      <c r="G81" s="39" t="s">
+      <c r="F81" s="37"/>
+      <c r="G81" s="40" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="82" spans="1:7">
-      <c r="A82" s="31" t="s">
+      <c r="A82" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="B82" s="31" t="s">
+      <c r="B82" s="32" t="s">
         <v>339</v>
       </c>
-      <c r="C82" s="32"/>
-      <c r="D82" s="31"/>
-      <c r="E82" s="31"/>
-      <c r="F82" s="31"/>
-      <c r="G82" s="31"/>
+      <c r="C82" s="33"/>
+      <c r="D82" s="32"/>
+      <c r="E82" s="32"/>
+      <c r="F82" s="32"/>
+      <c r="G82" s="32"/>
     </row>
     <row r="83" spans="1:7">
-      <c r="A83" s="31" t="s">
+      <c r="A83" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="B83" s="31" t="s">
+      <c r="B83" s="32" t="s">
         <v>340</v>
       </c>
-      <c r="C83" s="32"/>
-      <c r="D83" s="31"/>
-      <c r="E83" s="31"/>
-      <c r="F83" s="31"/>
-      <c r="G83" s="31"/>
+      <c r="C83" s="33"/>
+      <c r="D83" s="32"/>
+      <c r="E83" s="32"/>
+      <c r="F83" s="32"/>
+      <c r="G83" s="32"/>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="31" t="s">
+      <c r="A84" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="B84" s="31" t="s">
+      <c r="B84" s="32" t="s">
         <v>341</v>
       </c>
-      <c r="C84" s="32"/>
-      <c r="D84" s="31"/>
-      <c r="E84" s="31"/>
-      <c r="F84" s="31"/>
-      <c r="G84" s="31"/>
+      <c r="C84" s="33"/>
+      <c r="D84" s="32"/>
+      <c r="E84" s="32"/>
+      <c r="F84" s="32"/>
+      <c r="G84" s="32"/>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="31" t="s">
+      <c r="A85" s="32" t="s">
         <v>227</v>
       </c>
-      <c r="B85" s="31" t="s">
+      <c r="B85" s="32" t="s">
         <v>342</v>
       </c>
-      <c r="C85" s="32"/>
-      <c r="D85" s="31"/>
-      <c r="E85" s="31"/>
-      <c r="F85" s="31"/>
-      <c r="G85" s="31"/>
+      <c r="C85" s="33"/>
+      <c r="D85" s="32"/>
+      <c r="E85" s="32"/>
+      <c r="F85" s="32"/>
+      <c r="G85" s="32"/>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="31"/>
-      <c r="B86" s="31"/>
-      <c r="C86" s="32"/>
-      <c r="D86" s="31"/>
-      <c r="E86" s="31"/>
-      <c r="F86" s="31"/>
-      <c r="G86" s="31"/>
+      <c r="A86" s="32"/>
+      <c r="B86" s="32"/>
+      <c r="C86" s="33"/>
+      <c r="D86" s="32"/>
+      <c r="E86" s="32"/>
+      <c r="F86" s="32"/>
+      <c r="G86" s="32"/>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" s="31" t="s">
+      <c r="A87" s="32" t="s">
         <v>230</v>
       </c>
-      <c r="B87" s="31" t="s">
+      <c r="B87" s="32" t="s">
         <v>343</v>
       </c>
-      <c r="C87" s="32"/>
-      <c r="D87" s="31"/>
-      <c r="E87" s="31"/>
-      <c r="F87" s="31"/>
-      <c r="G87" s="31"/>
+      <c r="C87" s="33"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="32"/>
+      <c r="F87" s="32"/>
+      <c r="G87" s="32"/>
     </row>
     <row r="88" spans="1:7">
-      <c r="A88" s="31" t="s">
+      <c r="A88" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="B88" s="31" t="s">
+      <c r="B88" s="32" t="s">
         <v>344</v>
       </c>
-      <c r="C88" s="32"/>
-      <c r="D88" s="31"/>
-      <c r="E88" s="31"/>
-      <c r="F88" s="31"/>
-      <c r="G88" s="31"/>
+      <c r="C88" s="33"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="32"/>
+      <c r="F88" s="32"/>
+      <c r="G88" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6838,7 +6842,7 @@
       </c>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" ht="43.2" spans="1:8">
       <c r="A25" s="11">
         <v>57</v>
       </c>
@@ -6857,7 +6861,7 @@
       <c r="F25" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="20" t="s">
         <v>418</v>
       </c>
       <c r="H25" s="4"/>
@@ -6929,7 +6933,7 @@
       <c r="F28" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G28" s="20" t="s">
+      <c r="G28" s="21" t="s">
         <v>427</v>
       </c>
       <c r="H28" s="11"/>
@@ -6951,7 +6955,7 @@
         <v>354</v>
       </c>
       <c r="F29" s="3"/>
-      <c r="G29" s="20"/>
+      <c r="G29" s="21"/>
       <c r="H29" s="11"/>
     </row>
     <row r="30" spans="1:8">
@@ -6973,7 +6977,7 @@
       <c r="F30" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G30" s="20" t="s">
+      <c r="G30" s="21" t="s">
         <v>432</v>
       </c>
       <c r="H30" s="15" t="s">
@@ -6997,7 +7001,7 @@
         <v>354</v>
       </c>
       <c r="F31" s="3"/>
-      <c r="G31" s="20"/>
+      <c r="G31" s="21"/>
       <c r="H31" s="17"/>
     </row>
     <row r="32" spans="1:8">
@@ -7331,13 +7335,13 @@
       <c r="D46" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="E46" s="21" t="s">
+      <c r="E46" s="22" t="s">
         <v>364</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G46" s="22" t="s">
+      <c r="G46" s="23" t="s">
         <v>371</v>
       </c>
       <c r="H46" s="4"/>
@@ -7387,7 +7391,7 @@
       <c r="F48" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="G48" s="23" t="s">
+      <c r="G48" s="24" t="s">
         <v>478</v>
       </c>
       <c r="H48" s="11"/>
@@ -7409,7 +7413,7 @@
         <v>364</v>
       </c>
       <c r="F49" s="17"/>
-      <c r="G49" s="24"/>
+      <c r="G49" s="25"/>
       <c r="H49" s="11"/>
     </row>
     <row r="50" spans="1:8">
@@ -7431,7 +7435,7 @@
       <c r="F50" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="G50" s="23" t="s">
+      <c r="G50" s="24" t="s">
         <v>483</v>
       </c>
       <c r="H50" s="11"/>
@@ -7453,7 +7457,7 @@
         <v>364</v>
       </c>
       <c r="F51" s="17"/>
-      <c r="G51" s="24"/>
+      <c r="G51" s="25"/>
       <c r="H51" s="11"/>
     </row>
     <row r="52" spans="1:8">
@@ -7473,10 +7477,10 @@
       <c r="B53" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="C53" s="25" t="s">
+      <c r="C53" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D53" s="25" t="s">
+      <c r="D53" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E53" s="11"/>
@@ -7491,10 +7495,10 @@
       <c r="B54" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="C54" s="25" t="s">
+      <c r="C54" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D54" s="25" t="s">
+      <c r="D54" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E54" s="11"/>
@@ -7509,10 +7513,10 @@
       <c r="B55" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="C55" s="25" t="s">
+      <c r="C55" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D55" s="25" t="s">
+      <c r="D55" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E55" s="11"/>
@@ -7527,10 +7531,10 @@
       <c r="B56" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="C56" s="25" t="s">
+      <c r="C56" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D56" s="25" t="s">
+      <c r="D56" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E56" s="11"/>
@@ -7545,10 +7549,10 @@
       <c r="B57" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="C57" s="25" t="s">
+      <c r="C57" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D57" s="25" t="s">
+      <c r="D57" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E57" s="11"/>
@@ -7563,10 +7567,10 @@
       <c r="B58" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="C58" s="25" t="s">
+      <c r="C58" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D58" s="25" t="s">
+      <c r="D58" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E58" s="11"/>
@@ -7581,10 +7585,10 @@
       <c r="B59" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="C59" s="25" t="s">
+      <c r="C59" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D59" s="25" t="s">
+      <c r="D59" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E59" s="11"/>
@@ -7599,10 +7603,10 @@
       <c r="B60" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="C60" s="25" t="s">
+      <c r="C60" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D60" s="25" t="s">
+      <c r="D60" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E60" s="11"/>
@@ -7617,10 +7621,10 @@
       <c r="B61" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="C61" s="25" t="s">
+      <c r="C61" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D61" s="25" t="s">
+      <c r="D61" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E61" s="11"/>
@@ -7635,10 +7639,10 @@
       <c r="B62" s="11" t="s">
         <v>494</v>
       </c>
-      <c r="C62" s="25" t="s">
+      <c r="C62" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D62" s="25" t="s">
+      <c r="D62" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E62" s="11"/>
@@ -7653,10 +7657,10 @@
       <c r="B63" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="C63" s="25" t="s">
+      <c r="C63" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D63" s="25" t="s">
+      <c r="D63" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E63" s="11"/>
@@ -7671,10 +7675,10 @@
       <c r="B64" s="11" t="s">
         <v>496</v>
       </c>
-      <c r="C64" s="25" t="s">
+      <c r="C64" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D64" s="25" t="s">
+      <c r="D64" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E64" s="11"/>
@@ -7689,10 +7693,10 @@
       <c r="B65" s="11" t="s">
         <v>497</v>
       </c>
-      <c r="C65" s="25" t="s">
+      <c r="C65" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D65" s="25" t="s">
+      <c r="D65" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E65" s="11"/>
@@ -7707,10 +7711,10 @@
       <c r="B66" s="11" t="s">
         <v>498</v>
       </c>
-      <c r="C66" s="25" t="s">
+      <c r="C66" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D66" s="25" t="s">
+      <c r="D66" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E66" s="11"/>
@@ -7725,10 +7729,10 @@
       <c r="B67" s="11" t="s">
         <v>499</v>
       </c>
-      <c r="C67" s="25" t="s">
+      <c r="C67" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D67" s="25" t="s">
+      <c r="D67" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E67" s="11"/>
@@ -7743,7 +7747,7 @@
       <c r="B68" s="11" t="s">
         <v>500</v>
       </c>
-      <c r="C68" s="25" t="s">
+      <c r="C68" s="26" t="s">
         <v>409</v>
       </c>
       <c r="D68" s="11" t="s">
@@ -7767,10 +7771,10 @@
       <c r="B69" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="C69" s="25" t="s">
+      <c r="C69" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D69" s="25" t="s">
+      <c r="D69" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E69" s="11"/>
@@ -7785,10 +7789,10 @@
       <c r="B70" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="C70" s="25" t="s">
+      <c r="C70" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="D70" s="25" t="s">
+      <c r="D70" s="26" t="s">
         <v>409</v>
       </c>
       <c r="E70" s="11"/>
